--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="425">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -1267,6 +1267,42 @@
   </si>
   <si>
     <t>A programme float (Modifiers PROG-FLOAT) is added to give a realistic completion date alongside the best-case date. Float increases with the weight of the risk register.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecology / bat survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3.8 = Ecological features OR roof scope on a pre-2000 building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal: emergence surveys May–September only. A miss can cost a full year. Weeks illustrative (v4.4) — set from experience.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BuildingSafety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building Safety Regulator — Gateway 2 approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher-risk building (derived from Section 1: 18 m+ or 7+ storeys, residential-type use)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statutory 12 weeks, sequential after Stage 4 and Building Control, before tender award. Real-world determinations frequently exceed 20 weeks. Weeks illustrative (v4.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.4  ·  September 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added Durations rows SV7 (ecology / bat survey, parallel, 2–4 wks) and BS1 (Building Safety Regulator Gateway 2, critical, 12–24 wks), from docs/workbook-changes-sept-2026.md. Weeks illustrative. Found by the 21-report test run: the Gateway 2 and ecology stages the code supports never appeared because these rows were missing.</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1725,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2012,6 +2048,14 @@
       </c>
       <c r="B41" s="2" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -2025,7 +2069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -4007,6 +4051,136 @@
       </c>
       <c r="U34" s="7" t="s">
         <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D35" s="7">
+        <v>2</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4</v>
+      </c>
+      <c r="F35" s="7">
+        <v>2</v>
+      </c>
+      <c r="G35" s="7">
+        <v>4</v>
+      </c>
+      <c r="H35" s="7">
+        <v>2</v>
+      </c>
+      <c r="I35" s="7">
+        <v>4</v>
+      </c>
+      <c r="J35" s="7">
+        <v>2</v>
+      </c>
+      <c r="K35" s="7">
+        <v>4</v>
+      </c>
+      <c r="L35" s="7">
+        <v>2</v>
+      </c>
+      <c r="M35" s="7">
+        <v>4</v>
+      </c>
+      <c r="N35" s="7">
+        <v>2</v>
+      </c>
+      <c r="O35" s="7">
+        <v>4</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T35" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D36" s="7">
+        <v>12</v>
+      </c>
+      <c r="E36" s="7">
+        <v>24</v>
+      </c>
+      <c r="F36" s="7">
+        <v>12</v>
+      </c>
+      <c r="G36" s="7">
+        <v>24</v>
+      </c>
+      <c r="H36" s="7">
+        <v>12</v>
+      </c>
+      <c r="I36" s="7">
+        <v>24</v>
+      </c>
+      <c r="J36" s="7">
+        <v>12</v>
+      </c>
+      <c r="K36" s="7">
+        <v>24</v>
+      </c>
+      <c r="L36" s="7">
+        <v>12</v>
+      </c>
+      <c r="M36" s="7">
+        <v>24</v>
+      </c>
+      <c r="N36" s="7">
+        <v>12</v>
+      </c>
+      <c r="O36" s="7">
+        <v>24</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="S36" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T36" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -1743,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1760,8 +1760,10 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>422</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v4.5  ·  October 2026  ·  Nabil Kayali</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -1834,19 +1836,31 @@
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3,000 – 10,000 m²</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S7</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt; 10,000 m²  (Construction sheet only — a blank S7 cell, and every Durations row, falls back to S6)</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 250 m² boundary now falls cleanly on the S2/S3 line, so the Stage 3 gateway split works without a special case.</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -1858,8 +1872,10 @@
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>23</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pick the size band (S1-S7) from Q1.5 GIFA.</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1906,8 +1922,10 @@
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>35</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apply construction uplifts from Modifiers to the Construction duration only: access (ACC, highest tier) × the HIGHER of occupation (OCC) and phasing (PH-1) — occupation and phasing are not stacked.</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2056,6 +2074,18 @@
       </c>
       <c r="B43" s="2" t="s">
         <v>424</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v4.5</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Durations checked against eight University of Warwick projects (Oct 2026: Riley Court, Lakeside, Claycroft, Whitefields, Co-op, Scarman, IBRB café, Computer Science). Handover CH1 cut to 0–3 wks (commissioning runs inside construction; 2 wks on Lakeside, Riley Court and Whitefields). Fit-out CF2 S1–S4 shortened (Co-op 885 m² 7 wks; IBRB café ≈ 3 wks). M&amp;E refurb CR1 S1–S2 shortened (Scarman 5 wks). New size band S7 &gt; 10,000 m² with CR1 S7 50–70 (Claycroft 17,172 m²: 74 wks planned, forecast ≈ 95). Occupation and phasing uplifts no longer multiply — the higher applies (Lakeside: occupied, 6 sections, 45 wks). Confirmed unchanged: tender TN1 10–14 (Lakeside 13 wks to award), demolition CD1 (Whitefields ≈ 14 wks), CR1 S6 (Riley Court 36 + 6 wks strip-out), planning PL1 (Riley Court 7 wks).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4199,16 +4229,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="52" customWidth="1"/>
+    <col min="3" max="17" width="6" customWidth="1"/>
+    <col min="18" max="18" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>59</v>
       </c>
@@ -4251,14 +4281,24 @@
       <c r="N1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S7_Lo</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S7_Hi</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>214</v>
       </c>
@@ -4301,14 +4341,14 @@
       <c r="N2" s="7">
         <v>84</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>217</v>
       </c>
@@ -4351,14 +4391,14 @@
       <c r="N3" s="7">
         <v>110</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>220</v>
       </c>
@@ -4401,14 +4441,14 @@
       <c r="N4" s="7">
         <v>72</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>223</v>
       </c>
@@ -4443,14 +4483,14 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
-      <c r="O5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="R5" s="7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>226</v>
       </c>
@@ -4493,14 +4533,14 @@
       <c r="N6" s="7">
         <v>72</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="Q6" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="R6" s="7" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>229</v>
       </c>
@@ -4508,16 +4548,16 @@
         <v>230</v>
       </c>
       <c r="C7" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="7">
         <v>8</v>
@@ -4543,14 +4583,22 @@
       <c r="N7" s="7">
         <v>50</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="7">
+        <v>50</v>
+      </c>
+      <c r="P7" s="7">
+        <v>70</v>
+      </c>
+      <c r="Q7" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P7" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full/partial services replacement. Longest refurb row — use when 3+ M&amp;E systems in q2_2. v4.5 (Oct 2026): S1–S2 shortened (Scarman toilets 71 m², 5-wk window); S7 (&gt;10,000 m²) added from Claycroft (17,172 m², Morgan Sindall: 74 wks works planned Jun 2025–Dec 2026, occupied, three blocks in turn). Riley Court 3,850 m² (S6): 36 wks + 6 wks strip-out = 42.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>232</v>
       </c>
@@ -4593,14 +4641,14 @@
       <c r="N8" s="7">
         <v>42</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="Q8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="R8" s="7" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>235</v>
       </c>
@@ -4643,14 +4691,14 @@
       <c r="N9" s="7">
         <v>46</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="Q9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="R9" s="7" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>238</v>
       </c>
@@ -4658,28 +4706,28 @@
         <v>239</v>
       </c>
       <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4</v>
+      </c>
+      <c r="E10" s="7">
         <v>3</v>
       </c>
-      <c r="D10" s="7">
+      <c r="F10" s="7">
         <v>5</v>
       </c>
-      <c r="E10" s="7">
-        <v>4</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="G10" s="7">
+        <v>4</v>
+      </c>
+      <c r="H10" s="7">
+        <v>7</v>
+      </c>
+      <c r="I10" s="7">
         <v>6</v>
       </c>
-      <c r="G10" s="7">
-        <v>6</v>
-      </c>
-      <c r="H10" s="7">
-        <v>10</v>
-      </c>
-      <c r="I10" s="7">
-        <v>10</v>
-      </c>
       <c r="J10" s="7">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K10" s="7">
         <v>16</v>
@@ -4693,14 +4741,16 @@
       <c r="N10" s="7">
         <v>38</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="Q10" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P10" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard offices/academic/retail/café. Partitions, ceiling, floor, M&amp;E 1st+2nd fix. v4.5 (Oct 2026): S1–S4 shortened — Co-op store 885 m² 7 wks (Kingfisher, 2 of them 7-day working), IBRB café 72 m² ≈ 3 wks (Senevo prelims).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>241</v>
       </c>
@@ -4743,14 +4793,14 @@
       <c r="N11" s="7">
         <v>60</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="Q11" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="R11" s="7" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>244</v>
       </c>
@@ -4793,14 +4843,14 @@
       <c r="N12" s="7">
         <v>22</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="Q12" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="R12" s="7" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>247</v>
       </c>
@@ -4843,14 +4893,14 @@
       <c r="N13" s="7">
         <v>18</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="Q13" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P13" s="7" t="s">
+      <c r="R13" s="7" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>250</v>
       </c>
@@ -4858,46 +4908,48 @@
         <v>251</v>
       </c>
       <c r="C14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7">
         <v>1</v>
       </c>
       <c r="E14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" s="7">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7">
+        <v>2</v>
+      </c>
+      <c r="K14" s="7">
+        <v>2</v>
+      </c>
+      <c r="L14" s="7">
+        <v>2</v>
+      </c>
+      <c r="M14" s="7">
+        <v>2</v>
+      </c>
+      <c r="N14" s="7">
         <v>3</v>
       </c>
-      <c r="J14" s="7">
-        <v>6</v>
-      </c>
-      <c r="K14" s="7">
-        <v>4</v>
-      </c>
-      <c r="L14" s="7">
-        <v>8</v>
-      </c>
-      <c r="M14" s="7">
-        <v>6</v>
-      </c>
-      <c r="N14" s="7">
-        <v>10</v>
-      </c>
-      <c r="O14" s="7" t="s">
+      <c r="Q14" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>252</v>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Always added to construction. Snagging, Practical Completion, O&amp;M manuals and client move-in only — commissioning runs inside the last weeks of construction. v4.5 (Oct 2026): 2 wks on Lakeside (tender programme), Riley Court (Maris) and Whitefields (H&amp;S file); was up to 6-10 wks.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5076,8 +5128,10 @@
       <c r="F7" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>284</v>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access mgmt, phasing, noise/dust, supervision. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5099,8 +5153,10 @@
       <c r="F8" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>288</v>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial decant / zoned works. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5145,8 +5201,10 @@
       <c r="F10" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>296</v>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sequential handovers extend site duration. v4.5 (Oct 2026): when occupation (OCC-1/OCC-2) also applies, only the HIGHER of the two is used — they no longer multiply. Lakeside (occupied, 6 sections, 45 wks) ran about 10% slower than Riley Court vacant.</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252A6877-6FEF-40EE-8821-DC895BA996C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1045C2D1-FE5F-4001-A40E-A7D1F245F6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="458">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Version</t>
   </si>
   <si>
-    <t>v4.3  ·  June 2026  ·  Nabil Kayali</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>S6</t>
   </si>
   <si>
-    <t>&gt; 3,000 m²</t>
-  </si>
-  <si>
     <t>The 250 m² boundary now falls cleanly on the S2/S3 line, so the Stage 3 gateway split works without a special case.</t>
   </si>
   <si>
@@ -96,9 +90,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>Pick the size band (S1-S6) from Q1.5 GIFA.</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -130,9 +121,6 @@
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>Apply construction uplifts (occupation, phasing) from Modifiers tab to the Construction duration only.</t>
   </si>
   <si>
     <t>8</t>
@@ -723,9 +711,6 @@
     <t>Refurb — M&amp;E Replacement</t>
   </si>
   <si>
-    <t>Full/partial services replacement. Longest refurb row — use when 3+ M&amp;E systems in q2_2.</t>
-  </si>
-  <si>
     <t>CR2</t>
   </si>
   <si>
@@ -750,9 +735,6 @@
     <t>Fit-Out — Basic / Cat A</t>
   </si>
   <si>
-    <t>Standard offices/academic. Partitions, ceiling, floor, M&amp;E 1st+2nd fix.</t>
-  </si>
-  <si>
     <t>CS1</t>
   </si>
   <si>
@@ -786,9 +768,6 @@
     <t>Handover</t>
   </si>
   <si>
-    <t>Commissioning, snagging, Practical Completion sign-off. Always added to construction.</t>
-  </si>
-  <si>
     <t>Modifier</t>
   </si>
   <si>
@@ -882,9 +861,6 @@
     <t>q3_6_occupation=Fully occupied</t>
   </si>
   <si>
-    <t>Access mgmt, phasing, noise/dust, supervision.</t>
-  </si>
-  <si>
     <t>OCC-2</t>
   </si>
   <si>
@@ -894,9 +870,6 @@
     <t>q3_6_occupation=Partially occupied</t>
   </si>
   <si>
-    <t>Partial decant / zoned works.</t>
-  </si>
-  <si>
     <t>OCC-3</t>
   </si>
   <si>
@@ -918,9 +891,6 @@
     <t>q4_6_phasing=Multiple phases</t>
   </si>
   <si>
-    <t>Sequential handovers extend site duration.</t>
-  </si>
-  <si>
     <t>FN-1</t>
   </si>
   <si>
@@ -966,9 +936,6 @@
     <t>Access uplift — low impact</t>
   </si>
   <si>
-    <t>q3_5_accessConstraints includes Restricted hours OR Shared access OR Height/weight limits OR Scaffold licence</t>
-  </si>
-  <si>
     <t>Site-logistics drag. Apply highest applicable ACC tier only (do not stack ACC-1+ACC-2). Cost side already in Prelims A (NRM1 Tab 3). Each selected constraint also seeds a LOW–MEDIUM risk-register entry — see risk map.</t>
   </si>
   <si>
@@ -978,12 +945,6 @@
     <t>Access uplift — high impact</t>
   </si>
   <si>
-    <t>q3_5_accessConstraints includes No vehicle access OR Term-time only</t>
-  </si>
-  <si>
-    <t>Major access restriction. Term-time-only fragments the programme across vacation windows — consider phasing (PH-1) and flag HIGH risk. Apply highest applicable ACC tier only. Each selected constraint seeds a MEDIUM–HIGH risk-register entry.</t>
-  </si>
-  <si>
     <t>PROG-FLOAT</t>
   </si>
   <si>
@@ -1269,40 +1230,178 @@
     <t>A programme float (Modifiers PROG-FLOAT) is added to give a realistic completion date alongside the best-case date. Float increases with the weight of the risk register.</t>
   </si>
   <si>
-    <t xml:space="preserve">SV7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecology / bat survey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3.8 = Ecological features OR roof scope on a pre-2000 building</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seasonal: emergence surveys May–September only. A miss can cost a full year. Weeks illustrative (v4.4) — set from experience.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BuildingSafety</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building Safety Regulator — Gateway 2 approval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Higher-risk building (derived from Section 1: 18 m+ or 7+ storeys, residential-type use)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statutory 12 weeks, sequential after Stage 4 and Building Control, before tender award. Real-world determinations frequently exceed 20 weeks. Weeks illustrative (v4.4).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v4.4  ·  September 2026  ·  Nabil Kayali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v4.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added Durations rows SV7 (ecology / bat survey, parallel, 2–4 wks) and BS1 (Building Safety Regulator Gateway 2, critical, 12–24 wks), from docs/workbook-changes-sept-2026.md. Weeks illustrative. Found by the 21-report test run: the Gateway 2 and ecology stages the code supports never appeared because these rows were missing.</t>
+    <t>SV7</t>
+  </si>
+  <si>
+    <t>Ecology / bat survey</t>
+  </si>
+  <si>
+    <t>Q3.8 = Ecological features OR roof scope on a pre-2000 building</t>
+  </si>
+  <si>
+    <t>Seasonal: emergence surveys May–September only. A miss can cost a full year. Weeks illustrative (v4.4) — set from experience.</t>
+  </si>
+  <si>
+    <t>BS1</t>
+  </si>
+  <si>
+    <t>BuildingSafety</t>
+  </si>
+  <si>
+    <t>Building Safety Regulator — Gateway 2 approval</t>
+  </si>
+  <si>
+    <t>Higher-risk building (derived from Section 1: 18 m+ or 7+ storeys, residential-type use)</t>
+  </si>
+  <si>
+    <t>Statutory 12 weeks, sequential after Stage 4 and Building Control, before tender award. Real-world determinations frequently exceed 20 weeks. Weeks illustrative (v4.4).</t>
+  </si>
+  <si>
+    <t>v4.4</t>
+  </si>
+  <si>
+    <t>Added Durations rows SV7 (ecology / bat survey, parallel, 2–4 wks) and BS1 (Building Safety Regulator Gateway 2, critical, 12–24 wks), from docs/workbook-changes-sept-2026.md. Weeks illustrative. Found by the 21-report test run: the Gateway 2 and ecology stages the code supports never appeared because these rows were missing.</t>
+  </si>
+  <si>
+    <t>3,000 – 10,000 m²</t>
+  </si>
+  <si>
+    <t>S7</t>
+  </si>
+  <si>
+    <t>&gt; 10,000 m²  (Construction sheet only — a blank S7 cell, and every Durations row, falls back to S6)</t>
+  </si>
+  <si>
+    <t>Pick the size band (S1-S7) from Q1.5 GIFA.</t>
+  </si>
+  <si>
+    <t>Apply construction uplifts from Modifiers to the Construction duration only: access (ACC, highest tier) × the HIGHER of occupation (OCC) and phasing (PH-1) — occupation and phasing are not stacked.</t>
+  </si>
+  <si>
+    <t>v4.5</t>
+  </si>
+  <si>
+    <t>Durations checked against eight University of Warwick projects (Oct 2026: Riley Court, Lakeside, Claycroft, Whitefields, Co-op, Scarman, IBRB café, Computer Science). Handover CH1 cut to 0–3 wks (commissioning runs inside construction; 2 wks on Lakeside, Riley Court and Whitefields). Fit-out CF2 S1–S4 shortened (Co-op 885 m² 7 wks; IBRB café ≈ 3 wks). M&amp;E refurb CR1 S1–S2 shortened (Scarman 5 wks). New size band S7 &gt; 10,000 m² with CR1 S7 50–70 (Claycroft 17,172 m²: 74 wks planned, forecast ≈ 95). Occupation and phasing uplifts no longer multiply — the higher applies (Lakeside: occupied, 6 sections, 45 wks). Confirmed unchanged: tender TN1 10–14 (Lakeside 13 wks to award), demolition CD1 (Whitefields ≈ 14 wks), CR1 S6 (Riley Court 36 + 6 wks strip-out), planning PL1 (Riley Court 7 wks).</t>
+  </si>
+  <si>
+    <t>S7_Lo</t>
+  </si>
+  <si>
+    <t>S7_Hi</t>
+  </si>
+  <si>
+    <t>Full/partial services replacement. Longest refurb row — use when 3+ M&amp;E systems in q2_2. v4.5 (Oct 2026): S1–S2 shortened (Scarman toilets 71 m², 5-wk window); S7 (&gt;10,000 m²) added from Claycroft (17,172 m², Morgan Sindall: 74 wks works planned Jun 2025–Dec 2026, occupied, three blocks in turn). Riley Court 3,850 m² (S6): 36 wks + 6 wks strip-out = 42.</t>
+  </si>
+  <si>
+    <t>Standard offices/academic/retail/café. Partitions, ceiling, floor, M&amp;E 1st+2nd fix. v4.5 (Oct 2026): S1–S4 shortened — Co-op store 885 m² 7 wks (Kingfisher, 2 of them 7-day working), IBRB café 72 m² ≈ 3 wks (Senevo prelims).</t>
+  </si>
+  <si>
+    <t>Always added to construction. Snagging, Practical Completion, O&amp;M manuals and client move-in only — commissioning runs inside the last weeks of construction. v4.5 (Oct 2026): 2 wks on Lakeside (tender programme), Riley Court (Maris) and Whitefields (H&amp;S file); was up to 6-10 wks.</t>
+  </si>
+  <si>
+    <t>Access mgmt, phasing, noise/dust, supervision. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
+  </si>
+  <si>
+    <t>Partial decant / zoned works. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
+  </si>
+  <si>
+    <t>Sequential handovers extend site duration. v4.5 (Oct 2026): when occupation (OCC-1/OCC-2) also applies, only the HIGHER of the two is used — they no longer multiply. Lakeside (occupied, 6 sections, 45 wks) ran about 10% slower than Riley Court vacant.</t>
+  </si>
+  <si>
+    <t>TN4</t>
+  </si>
+  <si>
+    <t>Tender — Negotiated (single contractor)</t>
+  </si>
+  <si>
+    <t>Procurement Reference route to market = Negotiated</t>
+  </si>
+  <si>
+    <t>Negotiation with one contractor on an agreed basis: no competition period, only pricing, review and award. Added v4.6 (Oct 2026) — the negotiated route used to take the 10–14 week formal tender (TN1).</t>
+  </si>
+  <si>
+    <t>q3_5 includes Restricted working hours OR Access routes shared OR Tight site OR Site fronts a public road (old labels: Restricted hours, Shared access, Height/weight limits, Scaffold licence)</t>
+  </si>
+  <si>
+    <t>q3_5 includes Restricted deliveries or no vehicle access</t>
+  </si>
+  <si>
+    <t>Major access restriction. Apply the highest ACC tier only. Since v4.6, works limited to certain periods (Q3.5 + Q3.5a) take no uplift: the construction is fitted into the allowed windows instead (HOL rows below for school holidays).</t>
+  </si>
+  <si>
+    <t>HOL-1</t>
+  </si>
+  <si>
+    <t>School holiday — summer</t>
+  </si>
+  <si>
+    <t>Construction window</t>
+  </si>
+  <si>
+    <t>WINDOW</t>
+  </si>
+  <si>
+    <t>07-22/09-01</t>
+  </si>
+  <si>
+    <t>q3_5a_workWindow = School / university holidays only</t>
+  </si>
+  <si>
+    <t>MM-DD/MM-DD, typical England school holidays. Construction weeks are fitted into these windows; a week counts when its middle day falls inside one. Added v4.6 (Oct 2026).</t>
+  </si>
+  <si>
+    <t>HOL-2</t>
+  </si>
+  <si>
+    <t>School holiday — Christmas</t>
+  </si>
+  <si>
+    <t>12-20/01-03</t>
+  </si>
+  <si>
+    <t>HOL-3</t>
+  </si>
+  <si>
+    <t>School holiday — Easter (moves each year; check the dates)</t>
+  </si>
+  <si>
+    <t>03-29/04-12</t>
+  </si>
+  <si>
+    <t>HOL-4</t>
+  </si>
+  <si>
+    <t>School holiday — October half-term</t>
+  </si>
+  <si>
+    <t>10-24/11-01</t>
+  </si>
+  <si>
+    <t>HOL-5</t>
+  </si>
+  <si>
+    <t>School holiday — February half-term</t>
+  </si>
+  <si>
+    <t>02-13/02-21</t>
+  </si>
+  <si>
+    <t>HOL-6</t>
+  </si>
+  <si>
+    <t>School holiday — May half-term</t>
+  </si>
+  <si>
+    <t>05-23/05-31</t>
+  </si>
+  <si>
+    <t>v4.6  ·  October 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t>v4.6</t>
+  </si>
+  <si>
+    <t>Pre-launch fixes (10 Oct 2026, test batch 3): TN4 negotiated tender (2–5 wks); ACC-1 / ACC-2 triggers follow the new Q3.5 wording; works limited to certain periods no longer take ACC-2 — the construction is fitted into the Q3.5a window, with HOL-1…HOL-6 (typical school holidays) on Modifiers.</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1478,6 +1577,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1743,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1760,18 +1862,16 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v4.5  ·  October 2026  ·  Nabil Kayali</t>
-        </is>
+      <c r="B2" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1780,168 +1880,156 @@
     </row>
     <row r="5" spans="1:2" ht="32.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3,000 – 10,000 m²</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S7</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&gt; 10,000 m²  (Construction sheet only — a blank S7 cell, and every Durations row, falls back to S6)</t>
-        </is>
+      <c r="A13" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 250 m² boundary now falls cleanly on the S2/S3 line, so the Stage 3 gateway split works without a special case.</t>
-        </is>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pick the size band (S1-S7) from Q1.5 GIFA.</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Apply construction uplifts from Modifiers to the Construction duration only: access (ACC, highest tier) × the HIGHER of occupation (OCC) and phasing (PH-1) — occupation and phasing are not stacked.</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1950,32 +2038,32 @@
     </row>
     <row r="26" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1984,108 +2072,112 @@
     </row>
     <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B31" s="4"/>
     </row>
     <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v4.5</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Durations checked against eight University of Warwick projects (Oct 2026: Riley Court, Lakeside, Claycroft, Whitefields, Co-op, Scarman, IBRB café, Computer Science). Handover CH1 cut to 0–3 wks (commissioning runs inside construction; 2 wks on Lakeside, Riley Court and Whitefields). Fit-out CF2 S1–S4 shortened (Co-op 885 m² 7 wks; IBRB café ≈ 3 wks). M&amp;E refurb CR1 S1–S2 shortened (Scarman 5 wks). New size band S7 &gt; 10,000 m² with CR1 S7 50–70 (Claycroft 17,172 m²: 74 wks planned, forecast ≈ 95). Occupation and phasing uplifts no longer multiply — the higher applies (Lakeside: occupied, 6 sections, 45 wks). Confirmed unchanged: tender TN1 10–14 (Lakeside 13 wks to award), demolition CD1 (Whitefields ≈ 14 wks), CR1 S6 (Riley Court 36 + 6 wks strip-out), planning PL1 (Riley Court 7 wks).</t>
-        </is>
+      <c r="A44" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2115,72 +2207,72 @@
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2205,13 +2297,13 @@
     </row>
     <row r="3" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D3" s="7">
         <v>0</v>
@@ -2250,33 +2342,33 @@
         <v>3</v>
       </c>
       <c r="P3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="32.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
@@ -2315,33 +2407,33 @@
         <v>4</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
@@ -2380,33 +2472,33 @@
         <v>3</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D6" s="7">
         <v>1</v>
@@ -2445,33 +2537,33 @@
         <v>3</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D7" s="7">
         <v>1</v>
@@ -2510,33 +2602,33 @@
         <v>3</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D8" s="7">
         <v>4</v>
@@ -2575,27 +2667,27 @@
         <v>10</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2620,13 +2712,13 @@
     </row>
     <row r="10" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D10" s="7">
         <v>1</v>
@@ -2665,33 +2757,33 @@
         <v>12</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="U10" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D11" s="7">
         <v>1</v>
@@ -2730,33 +2822,33 @@
         <v>3</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D12" s="7">
         <v>2</v>
@@ -2795,33 +2887,33 @@
         <v>4</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
@@ -2860,33 +2952,33 @@
         <v>14</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D14" s="7">
         <v>1</v>
@@ -2925,33 +3017,33 @@
         <v>3</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D15" s="7">
         <v>1</v>
@@ -2990,33 +3082,33 @@
         <v>3</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D16" s="7">
         <v>2</v>
@@ -3055,33 +3147,33 @@
         <v>14</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D17" s="7">
         <v>1</v>
@@ -3120,27 +3212,27 @@
         <v>4</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -3165,13 +3257,13 @@
     </row>
     <row r="19" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D19" s="7">
         <v>1</v>
@@ -3210,33 +3302,33 @@
         <v>2</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
@@ -3275,27 +3367,27 @@
         <v>2</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -3320,13 +3412,13 @@
     </row>
     <row r="22" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D22" s="7">
         <v>8</v>
@@ -3365,33 +3457,33 @@
         <v>13</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D23" s="7">
         <v>8</v>
@@ -3430,33 +3522,33 @@
         <v>13</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R23" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D24" s="7">
         <v>4</v>
@@ -3495,33 +3587,33 @@
         <v>8</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D25" s="7">
         <v>8</v>
@@ -3560,33 +3652,33 @@
         <v>13</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D26" s="7">
         <v>4</v>
@@ -3625,33 +3717,33 @@
         <v>6</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D27" s="7">
         <v>0</v>
@@ -3690,27 +3782,27 @@
         <v>0</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -3735,13 +3827,13 @@
     </row>
     <row r="29" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D29" s="7">
         <v>2</v>
@@ -3780,33 +3872,33 @@
         <v>10</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U29" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D30" s="7">
         <v>3</v>
@@ -3845,27 +3937,27 @@
         <v>5</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="S30" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -3890,13 +3982,13 @@
     </row>
     <row r="32" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D32" s="7">
         <v>6</v>
@@ -3935,33 +4027,33 @@
         <v>14</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="U32" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D33" s="7">
         <v>3</v>
@@ -4000,33 +4092,33 @@
         <v>6</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D34" s="7">
         <v>3</v>
@@ -4065,152 +4157,217 @@
         <v>6</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="U34" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="D35" s="7">
         <v>2</v>
       </c>
       <c r="E35" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="7">
         <v>2</v>
       </c>
       <c r="G35" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="7">
         <v>4</v>
       </c>
       <c r="J35" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" s="7">
         <v>4</v>
       </c>
       <c r="L35" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M35" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N35" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="D36" s="7">
+        <v>2</v>
+      </c>
+      <c r="E36" s="7">
+        <v>4</v>
+      </c>
+      <c r="F36" s="7">
+        <v>2</v>
+      </c>
+      <c r="G36" s="7">
+        <v>4</v>
+      </c>
+      <c r="H36" s="7">
+        <v>2</v>
+      </c>
+      <c r="I36" s="7">
+        <v>4</v>
+      </c>
+      <c r="J36" s="7">
+        <v>2</v>
+      </c>
+      <c r="K36" s="7">
+        <v>4</v>
+      </c>
+      <c r="L36" s="7">
+        <v>2</v>
+      </c>
+      <c r="M36" s="7">
+        <v>4</v>
+      </c>
+      <c r="N36" s="7">
+        <v>2</v>
+      </c>
+      <c r="O36" s="7">
+        <v>4</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S36" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T36" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D37" s="7">
         <v>12</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E37" s="7">
         <v>24</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F37" s="7">
         <v>12</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G37" s="7">
         <v>24</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H37" s="7">
         <v>12</v>
       </c>
-      <c r="I36" s="7">
+      <c r="I37" s="7">
         <v>24</v>
       </c>
-      <c r="J36" s="7">
+      <c r="J37" s="7">
         <v>12</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K37" s="7">
         <v>24</v>
       </c>
-      <c r="L36" s="7">
+      <c r="L37" s="7">
         <v>12</v>
       </c>
-      <c r="M36" s="7">
+      <c r="M37" s="7">
         <v>24</v>
       </c>
-      <c r="N36" s="7">
+      <c r="N37" s="7">
         <v>12</v>
       </c>
-      <c r="O36" s="7">
+      <c r="O37" s="7">
         <v>24</v>
       </c>
-      <c r="P36" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q36" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="R36" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="S36" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T36" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="U36" s="7" t="s">
-        <v>421</v>
+      <c r="P37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T37" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4240,70 +4397,66 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S7_Lo</t>
-        </is>
-      </c>
-      <c r="P1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S7_Hi</t>
-        </is>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="R1" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C2" s="6">
         <v>14</v>
@@ -4342,18 +4495,18 @@
         <v>84</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C3" s="6">
         <v>18</v>
@@ -4392,18 +4545,18 @@
         <v>110</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C4" s="6">
         <v>6</v>
@@ -4442,18 +4595,18 @@
         <v>72</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C5" s="6">
         <v>7</v>
@@ -4484,18 +4637,18 @@
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="Q5" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C6" s="6">
         <v>10</v>
@@ -4534,18 +4687,18 @@
         <v>72</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C7" s="6">
         <v>3</v>
@@ -4590,20 +4743,18 @@
         <v>70</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full/partial services replacement. Longest refurb row — use when 3+ M&amp;E systems in q2_2. v4.5 (Oct 2026): S1–S2 shortened (Scarman toilets 71 m², 5-wk window); S7 (&gt;10,000 m²) added from Claycroft (17,172 m², Morgan Sindall: 74 wks works planned Jun 2025–Dec 2026, occupied, three blocks in turn). Riley Court 3,850 m² (S6): 36 wks + 6 wks strip-out = 42.</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C8" s="6">
         <v>3</v>
@@ -4642,18 +4793,18 @@
         <v>42</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C9" s="6">
         <v>4</v>
@@ -4692,18 +4843,18 @@
         <v>46</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C10" s="6">
         <v>2</v>
@@ -4742,20 +4893,18 @@
         <v>38</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Standard offices/academic/retail/café. Partitions, ceiling, floor, M&amp;E 1st+2nd fix. v4.5 (Oct 2026): S1–S4 shortened — Co-op store 885 m² 7 wks (Kingfisher, 2 of them 7-day working), IBRB café 72 m² ≈ 3 wks (Senevo prelims).</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C11" s="6">
         <v>6</v>
@@ -4794,18 +4943,18 @@
         <v>60</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C12" s="6">
         <v>2</v>
@@ -4844,18 +4993,18 @@
         <v>22</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -4894,18 +5043,18 @@
         <v>18</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C14" s="6">
         <v>0</v>
@@ -4944,12 +5093,10 @@
         <v>3</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Always added to construction. Snagging, Practical Completion, O&amp;M manuals and client move-in only — commissioning runs inside the last weeks of construction. v4.5 (Oct 2026): 2 wks on Lakeside (tender programme), Riley Court (Maris) and Whitefields (H&amp;S file); was up to 6-10 wks.</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -4960,7 +5107,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4973,353 +5120,485 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E2" s="6">
         <v>0.5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E3" s="6">
         <v>0.7</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E5" s="6">
         <v>1.3</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E7" s="6">
         <v>0.3</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Access mgmt, phasing, noise/dust, supervision. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
-        </is>
+        <v>276</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E8" s="6">
         <v>0.2</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partial decant / zoned works. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
-        </is>
+        <v>279</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E9" s="6">
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E10" s="6">
         <v>0.15</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sequential handovers extend site duration. v4.5 (Oct 2026): when occupation (OCC-1/OCC-2) also applies, only the HIGHER of the two is used — they no longer multiply. Lakeside (occupied, 6 sections, 45 wks) ran about 10% slower than Riley Court vacant.</t>
-        </is>
+        <v>286</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E12" s="6">
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B13" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C13" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D13" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E13">
         <v>0.1</v>
       </c>
       <c r="F13" t="s">
-        <v>312</v>
+        <v>430</v>
       </c>
       <c r="G13" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="B14" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E14">
         <v>0.17499999999999999</v>
       </c>
       <c r="F14" t="s">
-        <v>316</v>
+        <v>431</v>
       </c>
       <c r="G14" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>324</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -5343,222 +5622,222 @@
   <sheetData>
     <row r="1" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5578,106 +5857,106 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1045C2D1-FE5F-4001-A40E-A7D1F245F6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EAA613-BD6D-414E-BC33-3C77CFA615CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="511">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -1395,13 +1395,172 @@
     <t>05-23/05-31</t>
   </si>
   <si>
-    <t>v4.6  ·  October 2026  ·  Nabil Kayali</t>
-  </si>
-  <si>
     <t>v4.6</t>
   </si>
   <si>
     <t>Pre-launch fixes (10 Oct 2026, test batch 3): TN4 negotiated tender (2–5 wks); ACC-1 / ACC-2 triggers follow the new Q3.5 wording; works limited to certain periods no longer take ACC-2 — the construction is fitted into the Q3.5a window, with HOL-1…HOL-6 (typical school holidays) on Modifiers.</t>
+  </si>
+  <si>
+    <t>SB-S1</t>
+  </si>
+  <si>
+    <t>Size band S1</t>
+  </si>
+  <si>
+    <t>Every duration row</t>
+  </si>
+  <si>
+    <t>SIZE BAND</t>
+  </si>
+  <si>
+    <t>&lt; 150</t>
+  </si>
+  <si>
+    <t>GIFA (external area on External works only)</t>
+  </si>
+  <si>
+    <t>Band = the first row whose limit the area meets, top to bottom. "&lt;" excludes the limit, "≤" includes it. Moved from the app code in v4.7.</t>
+  </si>
+  <si>
+    <t>SB-S2</t>
+  </si>
+  <si>
+    <t>Size band S2</t>
+  </si>
+  <si>
+    <t>≤ 250</t>
+  </si>
+  <si>
+    <t>GIFA</t>
+  </si>
+  <si>
+    <t>SB-S3</t>
+  </si>
+  <si>
+    <t>Size band S3</t>
+  </si>
+  <si>
+    <t>≤ 500</t>
+  </si>
+  <si>
+    <t>SB-S4</t>
+  </si>
+  <si>
+    <t>Size band S4</t>
+  </si>
+  <si>
+    <t>≤ 1500</t>
+  </si>
+  <si>
+    <t>SB-S5</t>
+  </si>
+  <si>
+    <t>Size band S5</t>
+  </si>
+  <si>
+    <t>≤ 3000</t>
+  </si>
+  <si>
+    <t>SB-S6</t>
+  </si>
+  <si>
+    <t>Size band S6</t>
+  </si>
+  <si>
+    <t>≤ 10000</t>
+  </si>
+  <si>
+    <t>SB-S7</t>
+  </si>
+  <si>
+    <t>Size band S7</t>
+  </si>
+  <si>
+    <t>&gt; 10000</t>
+  </si>
+  <si>
+    <t>S7 exists on the Construction sheet only; Durations rows use S6.</t>
+  </si>
+  <si>
+    <t>PB-S1</t>
+  </si>
+  <si>
+    <t>Programme check — S1 whole programme</t>
+  </si>
+  <si>
+    <t>Sense check</t>
+  </si>
+  <si>
+    <t>BENCHMARK</t>
+  </si>
+  <si>
+    <t>6-65</t>
+  </si>
+  <si>
+    <t>Weeks, min-max. A whole programme outside this range raises PROG_SHORT / PROG_LONG (a missing stage or a stage counted twice). Wide envelopes on purpose. Moved from the app code in v4.7.</t>
+  </si>
+  <si>
+    <t>PB-S2</t>
+  </si>
+  <si>
+    <t>Programme check — S2 whole programme</t>
+  </si>
+  <si>
+    <t>8-80</t>
+  </si>
+  <si>
+    <t>PB-S3</t>
+  </si>
+  <si>
+    <t>Programme check — S3 whole programme</t>
+  </si>
+  <si>
+    <t>10-100</t>
+  </si>
+  <si>
+    <t>PB-S4</t>
+  </si>
+  <si>
+    <t>Programme check — S4 whole programme</t>
+  </si>
+  <si>
+    <t>15-130</t>
+  </si>
+  <si>
+    <t>PB-S5</t>
+  </si>
+  <si>
+    <t>Programme check — S5 whole programme</t>
+  </si>
+  <si>
+    <t>25-160</t>
+  </si>
+  <si>
+    <t>PB-S6</t>
+  </si>
+  <si>
+    <t>Programme check — S6 whole programme</t>
+  </si>
+  <si>
+    <t>35-200</t>
+  </si>
+  <si>
+    <t>PB-S7</t>
+  </si>
+  <si>
+    <t>Programme check — S7 whole programme</t>
+  </si>
+  <si>
+    <t>45-260</t>
+  </si>
+  <si>
+    <t>v4.7  ·  October 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t>v4.7</t>
+  </si>
+  <si>
+    <t>No duration changed. Numbers the app used to hold in its code now live here: size-band limits SB-S1…SB-S7 and the whole-programme sense-check envelopes PB-S1…PB-S7 on Modifiers. The app no longer has backup durations: it refuses a workbook missing SV3–SV6, PL1, PL3–PL5, BC1, TN1, TN2, CH1 or any SB / PB row, and it no longer picks a tender from the project value on its own (the Procurement Reference decides; before that step the programme uses TN1, marked provisional).</t>
   </si>
 </sst>
 </file>
@@ -1556,6 +1715,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1577,9 +1739,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1845,7 +2004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1853,17 +2012,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2174,10 +2333,18 @@
     </row>
     <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>457</v>
+    </row>
+    <row r="46" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -2271,29 +2438,29 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="15"/>
     </row>
     <row r="3" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2686,29 +2853,29 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="15"/>
     </row>
     <row r="10" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -3231,29 +3398,29 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="15"/>
     </row>
     <row r="19" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -3386,29 +3553,29 @@
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
-      <c r="U21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="15"/>
     </row>
     <row r="22" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -3801,29 +3968,29 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="18"/>
     </row>
     <row r="29" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
@@ -3956,29 +4123,29 @@
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="13"/>
-      <c r="U31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="15"/>
     </row>
     <row r="32" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
@@ -5107,7 +5274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5476,7 +5643,7 @@
       <c r="D16" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="10" t="s">
         <v>437</v>
       </c>
       <c r="F16" s="6" t="s">
@@ -5499,7 +5666,7 @@
       <c r="D17" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="10" t="s">
         <v>442</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -5522,7 +5689,7 @@
       <c r="D18" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="10" t="s">
         <v>445</v>
       </c>
       <c r="F18" s="6" t="s">
@@ -5545,7 +5712,7 @@
       <c r="D19" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F19" s="6" t="s">
@@ -5568,7 +5735,7 @@
       <c r="D20" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="10" t="s">
         <v>451</v>
       </c>
       <c r="F20" s="6" t="s">
@@ -5591,7 +5758,7 @@
       <c r="D21" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="10" t="s">
         <v>454</v>
       </c>
       <c r="F21" s="6" t="s">
@@ -5600,6 +5767,306 @@
       <c r="G21" s="6" t="s">
         <v>439</v>
       </c>
+    </row>
+    <row r="22" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="G35" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EAA613-BD6D-414E-BC33-3C77CFA615CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8581785-52BB-4F5C-914A-43DBEE0B3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="527">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -957,9 +957,6 @@
     <t>UPLIFT_PCT_RULE</t>
   </si>
   <si>
-    <t>+1 wk per 13 wks</t>
-  </si>
-  <si>
     <t>Always</t>
   </si>
   <si>
@@ -1554,13 +1551,64 @@
     <t>45-260</t>
   </si>
   <si>
-    <t>v4.7  ·  October 2026  ·  Nabil Kayali</t>
-  </si>
-  <si>
     <t>v4.7</t>
   </si>
   <si>
     <t>No duration changed. Numbers the app used to hold in its code now live here: size-band limits SB-S1…SB-S7 and the whole-programme sense-check envelopes PB-S1…PB-S7 on Modifiers. The app no longer has backup durations: it refuses a workbook missing SV3–SV6, PL1, PL3–PL5, BC1, TN1, TN2, CH1 or any SB / PB row, and it no longer picks a tender from the project value on its own (the Procurement Reference decides; before that step the programme uses TN1, marked provisional).</t>
+  </si>
+  <si>
+    <t>DS2-DM</t>
+  </si>
+  <si>
+    <t>Stage 2 — Concept (demolition only)</t>
+  </si>
+  <si>
+    <t>Used instead of the building row for this project type</t>
+  </si>
+  <si>
+    <t>v4.8 (test batch 4): a demolition or external works job has short design stages, not a building's.</t>
+  </si>
+  <si>
+    <t>DS3-DM</t>
+  </si>
+  <si>
+    <t>Stage 3 — Developed (demolition only)</t>
+  </si>
+  <si>
+    <t>DS4-DM</t>
+  </si>
+  <si>
+    <t>Stage 4 — Technical (demolition only)</t>
+  </si>
+  <si>
+    <t>DS2-EW</t>
+  </si>
+  <si>
+    <t>Stage 2 — Concept (external works only)</t>
+  </si>
+  <si>
+    <t>DS3-EW</t>
+  </si>
+  <si>
+    <t>Stage 3 — Developed (external works only)</t>
+  </si>
+  <si>
+    <t>DS4-EW</t>
+  </si>
+  <si>
+    <t>Stage 4 — Technical (external works only)</t>
+  </si>
+  <si>
+    <t>+1 wk per 26 wks</t>
+  </si>
+  <si>
+    <t>v4.8  ·  October 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t>v4.8</t>
+  </si>
+  <si>
+    <t>Durations shortened after test batch 4 (11 Oct 2026, 30 scenarios): formal tender TN1 8–10 wks up to 1,500 m² and 10–12 above (was 10–14); client gateways GW / GW3 1 wk for 150–1,500 m² (was 2); programme float PROG-FLOAT +1 wk per 26 (was 13); new design rows DS2/DS3/DS4-DM and -EW for demolition and external works only; construction CN3 industrial S4–S6 18–28 / 24–34 / 30–44 (was 22–36 / 32–52 / 48–72), CN1 S6 50–70 (was 60–84), CF1 S4 10–14 (was 12–20), CX1 single-storey extension S1–S4 10–14 / 14–20 / 18–24 / 22–30 (was 7–10 / 8–12 / 12–18 / 18–26), CX2 S2–S3 16–22 / 20–28 (was 12–18 / 18–26) so multi-storey stays above single-storey.</t>
   </si>
 </sst>
 </file>
@@ -2004,7 +2052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2022,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2096,15 +2144,15 @@
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2124,7 +2172,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2172,7 +2220,7 @@
         <v>31</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2317,34 +2365,42 @@
     </row>
     <row r="43" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -2358,7 +2414,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3397,497 +3453,537 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="15"/>
-    </row>
-    <row r="19" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2</v>
+      </c>
+      <c r="H18" s="7">
+        <v>1</v>
+      </c>
+      <c r="I18" s="7">
+        <v>2</v>
+      </c>
+      <c r="J18" s="7">
+        <v>1</v>
+      </c>
+      <c r="K18" s="7">
+        <v>2</v>
+      </c>
+      <c r="L18" s="7">
+        <v>2</v>
+      </c>
+      <c r="M18" s="7">
+        <v>3</v>
+      </c>
+      <c r="N18" s="7">
+        <v>2</v>
+      </c>
+      <c r="O18" s="7">
+        <v>3</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="T18" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>144</v>
+        <v>513</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>146</v>
+        <v>514</v>
       </c>
       <c r="D19" s="7">
         <v>1</v>
       </c>
       <c r="E19" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="7">
         <v>2</v>
       </c>
       <c r="G19" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="7">
         <v>2</v>
       </c>
       <c r="I19" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="7">
         <v>2</v>
       </c>
       <c r="K19" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M19" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N19" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P19" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="R19" s="7" t="s">
         <v>112</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>148</v>
+        <v>511</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>150</v>
+        <v>515</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>151</v>
+        <v>516</v>
       </c>
       <c r="D20" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" s="7">
         <v>2</v>
       </c>
       <c r="I20" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="7">
         <v>2</v>
       </c>
       <c r="K20" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N20" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P20" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="R20" s="7" t="s">
         <v>112</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>152</v>
+        <v>511</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="15"/>
-    </row>
-    <row r="22" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7">
+        <v>2</v>
+      </c>
+      <c r="H21" s="7">
+        <v>2</v>
+      </c>
+      <c r="I21" s="7">
+        <v>3</v>
+      </c>
+      <c r="J21" s="7">
+        <v>2</v>
+      </c>
+      <c r="K21" s="7">
+        <v>3</v>
+      </c>
+      <c r="L21" s="7">
+        <v>3</v>
+      </c>
+      <c r="M21" s="7">
+        <v>4</v>
+      </c>
+      <c r="N21" s="7">
+        <v>3</v>
+      </c>
+      <c r="O21" s="7">
+        <v>4</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="T21" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>155</v>
+        <v>519</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>157</v>
+        <v>520</v>
       </c>
       <c r="D22" s="7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F22" s="7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G22" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I22" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J22" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K22" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L22" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M22" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N22" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O22" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P22" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>160</v>
+        <v>511</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>162</v>
+        <v>521</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>163</v>
+        <v>522</v>
       </c>
       <c r="D23" s="7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F23" s="7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G23" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I23" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J23" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K23" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L23" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M23" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N23" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O23" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P23" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="R23" s="7" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>164</v>
+        <v>511</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="7">
-        <v>4</v>
-      </c>
-      <c r="E24" s="7">
-        <v>8</v>
-      </c>
-      <c r="F24" s="7">
-        <v>4</v>
-      </c>
-      <c r="G24" s="7">
-        <v>8</v>
-      </c>
-      <c r="H24" s="7">
-        <v>4</v>
-      </c>
-      <c r="I24" s="7">
-        <v>8</v>
-      </c>
-      <c r="J24" s="7">
-        <v>4</v>
-      </c>
-      <c r="K24" s="7">
-        <v>8</v>
-      </c>
-      <c r="L24" s="7">
-        <v>4</v>
-      </c>
-      <c r="M24" s="7">
-        <v>8</v>
-      </c>
-      <c r="N24" s="7">
-        <v>4</v>
-      </c>
-      <c r="O24" s="7">
-        <v>8</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T24" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>169</v>
-      </c>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="15"/>
     </row>
     <row r="25" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="D25" s="7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F25" s="7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G25" s="7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I25" s="7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J25" s="7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K25" s="7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L25" s="7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M25" s="7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N25" s="7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O25" s="7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P25" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="S25" s="7" t="s">
         <v>83</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="D26" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F26" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G26" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J26" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K26" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L26" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M26" s="7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N26" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O26" s="7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P26" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="R26" s="7" t="s">
         <v>112</v>
@@ -3896,302 +3992,342 @@
         <v>83</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B27" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="15"/>
+    </row>
+    <row r="28" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="7">
-        <v>0</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0</v>
-      </c>
-      <c r="F27" s="7">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7">
-        <v>0</v>
-      </c>
-      <c r="H27" s="7">
-        <v>0</v>
-      </c>
-      <c r="I27" s="7">
-        <v>0</v>
-      </c>
-      <c r="J27" s="7">
-        <v>0</v>
-      </c>
-      <c r="K27" s="7">
-        <v>0</v>
-      </c>
-      <c r="L27" s="7">
-        <v>0</v>
-      </c>
-      <c r="M27" s="7">
-        <v>0</v>
-      </c>
-      <c r="N27" s="7">
-        <v>0</v>
-      </c>
-      <c r="O27" s="7">
-        <v>0</v>
-      </c>
-      <c r="P27" s="7" t="s">
+      <c r="C28" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" s="7">
+        <v>8</v>
+      </c>
+      <c r="E28" s="7">
+        <v>13</v>
+      </c>
+      <c r="F28" s="7">
+        <v>8</v>
+      </c>
+      <c r="G28" s="7">
+        <v>13</v>
+      </c>
+      <c r="H28" s="7">
+        <v>8</v>
+      </c>
+      <c r="I28" s="7">
+        <v>13</v>
+      </c>
+      <c r="J28" s="7">
+        <v>8</v>
+      </c>
+      <c r="K28" s="7">
+        <v>13</v>
+      </c>
+      <c r="L28" s="7">
+        <v>8</v>
+      </c>
+      <c r="M28" s="7">
+        <v>13</v>
+      </c>
+      <c r="N28" s="7">
+        <v>8</v>
+      </c>
+      <c r="O28" s="7">
+        <v>13</v>
+      </c>
+      <c r="P28" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="Q27" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R27" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="S27" s="7" t="s">
+      <c r="Q28" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="S28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="T27" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="18"/>
+      <c r="T28" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="U28" s="7" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="29" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D29" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E29" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F29" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G29" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H29" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J29" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K29" s="7">
+        <v>13</v>
+      </c>
+      <c r="L29" s="7">
         <v>8</v>
       </c>
-      <c r="L29" s="7">
-        <v>5</v>
-      </c>
       <c r="M29" s="7">
+        <v>13</v>
+      </c>
+      <c r="N29" s="7">
         <v>8</v>
       </c>
-      <c r="N29" s="7">
-        <v>6</v>
-      </c>
       <c r="O29" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P29" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="S29" s="7" t="s">
         <v>83</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="U29" s="7" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="D30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M30" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P30" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="S30" s="7" t="s">
         <v>83</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="15"/>
-    </row>
-    <row r="32" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="7">
+        <v>8</v>
+      </c>
+      <c r="E31" s="7">
+        <v>13</v>
+      </c>
+      <c r="F31" s="7">
+        <v>8</v>
+      </c>
+      <c r="G31" s="7">
+        <v>13</v>
+      </c>
+      <c r="H31" s="7">
+        <v>8</v>
+      </c>
+      <c r="I31" s="7">
+        <v>13</v>
+      </c>
+      <c r="J31" s="7">
+        <v>8</v>
+      </c>
+      <c r="K31" s="7">
+        <v>13</v>
+      </c>
+      <c r="L31" s="7">
+        <v>8</v>
+      </c>
+      <c r="M31" s="7">
+        <v>13</v>
+      </c>
+      <c r="N31" s="7">
+        <v>8</v>
+      </c>
+      <c r="O31" s="7">
+        <v>13</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="R31" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T31" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="U31" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D32" s="7">
+        <v>4</v>
+      </c>
+      <c r="E32" s="7">
         <v>6</v>
       </c>
-      <c r="E32" s="7">
-        <v>8</v>
-      </c>
       <c r="F32" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G32" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I32" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J32" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K32" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L32" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M32" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N32" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O32" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P32" s="7" t="s">
         <v>80</v>
@@ -4206,63 +4342,63 @@
         <v>83</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="U32" s="7" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="D33" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G33" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I33" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J33" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L33" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M33" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N33" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O33" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P33" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="R33" s="7" t="s">
         <v>112</v>
@@ -4271,187 +4407,147 @@
         <v>83</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D34" s="7">
-        <v>3</v>
-      </c>
-      <c r="E34" s="7">
-        <v>4</v>
-      </c>
-      <c r="F34" s="7">
-        <v>4</v>
-      </c>
-      <c r="G34" s="7">
-        <v>5</v>
-      </c>
-      <c r="H34" s="7">
-        <v>4</v>
-      </c>
-      <c r="I34" s="7">
-        <v>5</v>
-      </c>
-      <c r="J34" s="7">
-        <v>4</v>
-      </c>
-      <c r="K34" s="7">
-        <v>6</v>
-      </c>
-      <c r="L34" s="7">
-        <v>4</v>
-      </c>
-      <c r="M34" s="7">
-        <v>6</v>
-      </c>
-      <c r="N34" s="7">
-        <v>4</v>
-      </c>
-      <c r="O34" s="7">
-        <v>6</v>
-      </c>
-      <c r="P34" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q34" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="R34" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="S34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T34" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="U34" s="7" t="s">
-        <v>207</v>
-      </c>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>426</v>
+        <v>184</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>427</v>
+        <v>186</v>
       </c>
       <c r="D35" s="7">
         <v>2</v>
       </c>
       <c r="E35" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="7">
         <v>2</v>
       </c>
       <c r="G35" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="7">
         <v>4</v>
       </c>
       <c r="J35" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K35" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L35" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M35" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N35" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O35" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P35" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>112</v>
+        <v>187</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>83</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>428</v>
+        <v>188</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>429</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>401</v>
+        <v>191</v>
       </c>
       <c r="D36" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H36" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N36" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>80</v>
@@ -4460,91 +4556,441 @@
         <v>81</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="S36" s="7" t="s">
         <v>83</v>
       </c>
       <c r="T36" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="15"/>
+    </row>
+    <row r="38" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="7">
+        <v>6</v>
+      </c>
+      <c r="E38" s="7">
+        <v>8</v>
+      </c>
+      <c r="F38" s="7">
+        <v>8</v>
+      </c>
+      <c r="G38" s="7">
+        <v>10</v>
+      </c>
+      <c r="H38" s="7">
+        <v>8</v>
+      </c>
+      <c r="I38" s="7">
+        <v>10</v>
+      </c>
+      <c r="J38" s="7">
+        <v>8</v>
+      </c>
+      <c r="K38" s="7">
+        <v>10</v>
+      </c>
+      <c r="L38" s="7">
+        <v>10</v>
+      </c>
+      <c r="M38" s="7">
+        <v>12</v>
+      </c>
+      <c r="N38" s="7">
+        <v>10</v>
+      </c>
+      <c r="O38" s="7">
+        <v>12</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R38" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S38" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T38" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="7">
+        <v>3</v>
+      </c>
+      <c r="E39" s="7">
+        <v>4</v>
+      </c>
+      <c r="F39" s="7">
+        <v>3</v>
+      </c>
+      <c r="G39" s="7">
+        <v>4</v>
+      </c>
+      <c r="H39" s="7">
+        <v>4</v>
+      </c>
+      <c r="I39" s="7">
+        <v>6</v>
+      </c>
+      <c r="J39" s="7">
+        <v>4</v>
+      </c>
+      <c r="K39" s="7">
+        <v>6</v>
+      </c>
+      <c r="L39" s="7">
+        <v>4</v>
+      </c>
+      <c r="M39" s="7">
+        <v>6</v>
+      </c>
+      <c r="N39" s="7">
+        <v>4</v>
+      </c>
+      <c r="O39" s="7">
+        <v>6</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R39" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T39" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" s="7">
+        <v>3</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4</v>
+      </c>
+      <c r="F40" s="7">
+        <v>4</v>
+      </c>
+      <c r="G40" s="7">
+        <v>5</v>
+      </c>
+      <c r="H40" s="7">
+        <v>4</v>
+      </c>
+      <c r="I40" s="7">
+        <v>5</v>
+      </c>
+      <c r="J40" s="7">
+        <v>4</v>
+      </c>
+      <c r="K40" s="7">
+        <v>6</v>
+      </c>
+      <c r="L40" s="7">
+        <v>4</v>
+      </c>
+      <c r="M40" s="7">
+        <v>6</v>
+      </c>
+      <c r="N40" s="7">
+        <v>4</v>
+      </c>
+      <c r="O40" s="7">
+        <v>6</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S40" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T40" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="D41" s="7">
+        <v>2</v>
+      </c>
+      <c r="E41" s="7">
+        <v>3</v>
+      </c>
+      <c r="F41" s="7">
+        <v>2</v>
+      </c>
+      <c r="G41" s="7">
+        <v>3</v>
+      </c>
+      <c r="H41" s="7">
+        <v>3</v>
+      </c>
+      <c r="I41" s="7">
+        <v>4</v>
+      </c>
+      <c r="J41" s="7">
+        <v>3</v>
+      </c>
+      <c r="K41" s="7">
+        <v>4</v>
+      </c>
+      <c r="L41" s="7">
+        <v>3</v>
+      </c>
+      <c r="M41" s="7">
+        <v>5</v>
+      </c>
+      <c r="N41" s="7">
+        <v>3</v>
+      </c>
+      <c r="O41" s="7">
+        <v>5</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R41" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T41" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="U41" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="D42" s="7">
+        <v>2</v>
+      </c>
+      <c r="E42" s="7">
+        <v>4</v>
+      </c>
+      <c r="F42" s="7">
+        <v>2</v>
+      </c>
+      <c r="G42" s="7">
+        <v>4</v>
+      </c>
+      <c r="H42" s="7">
+        <v>2</v>
+      </c>
+      <c r="I42" s="7">
+        <v>4</v>
+      </c>
+      <c r="J42" s="7">
+        <v>2</v>
+      </c>
+      <c r="K42" s="7">
+        <v>4</v>
+      </c>
+      <c r="L42" s="7">
+        <v>2</v>
+      </c>
+      <c r="M42" s="7">
+        <v>4</v>
+      </c>
+      <c r="N42" s="7">
+        <v>2</v>
+      </c>
+      <c r="O42" s="7">
+        <v>4</v>
+      </c>
+      <c r="P42" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q42" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R42" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S42" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T42" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="U42" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="U36" s="7" t="s">
+    </row>
+    <row r="43" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="B43" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="D43" s="7">
+        <v>12</v>
+      </c>
+      <c r="E43" s="7">
+        <v>24</v>
+      </c>
+      <c r="F43" s="7">
+        <v>12</v>
+      </c>
+      <c r="G43" s="7">
+        <v>24</v>
+      </c>
+      <c r="H43" s="7">
+        <v>12</v>
+      </c>
+      <c r="I43" s="7">
+        <v>24</v>
+      </c>
+      <c r="J43" s="7">
+        <v>12</v>
+      </c>
+      <c r="K43" s="7">
+        <v>24</v>
+      </c>
+      <c r="L43" s="7">
+        <v>12</v>
+      </c>
+      <c r="M43" s="7">
+        <v>24</v>
+      </c>
+      <c r="N43" s="7">
+        <v>12</v>
+      </c>
+      <c r="O43" s="7">
+        <v>24</v>
+      </c>
+      <c r="P43" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R43" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T43" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="D37" s="7">
-        <v>12</v>
-      </c>
-      <c r="E37" s="7">
-        <v>24</v>
-      </c>
-      <c r="F37" s="7">
-        <v>12</v>
-      </c>
-      <c r="G37" s="7">
-        <v>24</v>
-      </c>
-      <c r="H37" s="7">
-        <v>12</v>
-      </c>
-      <c r="I37" s="7">
-        <v>24</v>
-      </c>
-      <c r="J37" s="7">
-        <v>12</v>
-      </c>
-      <c r="K37" s="7">
-        <v>24</v>
-      </c>
-      <c r="L37" s="7">
-        <v>12</v>
-      </c>
-      <c r="M37" s="7">
-        <v>24</v>
-      </c>
-      <c r="N37" s="7">
-        <v>12</v>
-      </c>
-      <c r="O37" s="7">
-        <v>24</v>
-      </c>
-      <c r="P37" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q37" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="R37" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T37" s="7" t="s">
+      <c r="U43" s="7" t="s">
         <v>407</v>
-      </c>
-      <c r="U37" s="7" t="s">
-        <v>408</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A31:U31"/>
+    <mergeCell ref="A37:U37"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A9:U9"/>
-    <mergeCell ref="A18:U18"/>
-    <mergeCell ref="A21:U21"/>
-    <mergeCell ref="A28:U28"/>
+    <mergeCell ref="A24:U24"/>
+    <mergeCell ref="A27:U27"/>
+    <mergeCell ref="A34:U34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4606,10 +5052,10 @@
         <v>69</v>
       </c>
       <c r="O1" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>418</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>419</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>70</v>
@@ -4656,10 +5102,10 @@
         <v>64</v>
       </c>
       <c r="M2" s="7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N2" s="7">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>80</v>
@@ -4744,22 +5190,22 @@
         <v>22</v>
       </c>
       <c r="I4" s="7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J4" s="7">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K4" s="7">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L4" s="7">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="M4" s="7">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="N4" s="7">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="7" t="s">
         <v>80</v>
@@ -4776,28 +5222,28 @@
         <v>220</v>
       </c>
       <c r="C5" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F5" s="7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" s="7">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H5" s="7">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I5" s="7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J5" s="7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
@@ -4824,16 +5270,16 @@
         <v>14</v>
       </c>
       <c r="E6" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F6" s="7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H6" s="7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I6" s="7">
         <v>26</v>
@@ -4913,7 +5359,7 @@
         <v>80</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -4992,10 +5438,10 @@
         <v>12</v>
       </c>
       <c r="I9" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" s="7">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K9" s="7">
         <v>20</v>
@@ -5063,7 +5509,7 @@
         <v>80</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5263,7 +5709,7 @@
         <v>80</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -5443,7 +5889,7 @@
         <v>276</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5466,7 +5912,7 @@
         <v>279</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5512,7 +5958,7 @@
         <v>286</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5578,7 +6024,7 @@
         <v>0.1</v>
       </c>
       <c r="F13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G13" t="s">
         <v>302</v>
@@ -5601,10 +6047,10 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="F14" t="s">
+        <v>430</v>
+      </c>
+      <c r="G14" t="s">
         <v>431</v>
-      </c>
-      <c r="G14" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24" x14ac:dyDescent="0.25">
@@ -5621,450 +6067,450 @@
         <v>308</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="E16" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>442</v>
-      </c>
       <c r="F17" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>445</v>
-      </c>
       <c r="F18" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>448</v>
-      </c>
       <c r="F19" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>451</v>
-      </c>
       <c r="F20" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>454</v>
-      </c>
       <c r="F21" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="E22" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>467</v>
       </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>470</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>473</v>
-      </c>
       <c r="F25" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>476</v>
-      </c>
       <c r="F26" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>479</v>
-      </c>
       <c r="F27" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="C28" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E28" s="10" t="s">
+      <c r="F28" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="E29" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="F29" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>488</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>492</v>
-      </c>
       <c r="F30" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>495</v>
-      </c>
       <c r="F31" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E32" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>498</v>
-      </c>
       <c r="F32" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="C33" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>501</v>
-      </c>
       <c r="F33" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="C34" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>504</v>
-      </c>
       <c r="F34" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>507</v>
-      </c>
       <c r="F35" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G35" s="6"/>
     </row>
@@ -6089,222 +6535,222 @@
   <sheetData>
     <row r="1" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>316</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>346</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>352</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>363</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>366</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>181</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -6327,103 +6773,103 @@
         <v>5</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>376</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>378</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>380</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>382</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>384</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>386</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>388</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>390</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>392</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>394</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>398</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8581785-52BB-4F5C-914A-43DBEE0B3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514338E3-E2D9-43A9-9CEA-1DBD5BB77AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="551">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -1602,13 +1602,85 @@
     <t>+1 wk per 26 wks</t>
   </si>
   <si>
-    <t>v4.8  ·  October 2026  ·  Nabil Kayali</t>
-  </si>
-  <si>
     <t>v4.8</t>
   </si>
   <si>
     <t>Durations shortened after test batch 4 (11 Oct 2026, 30 scenarios): formal tender TN1 8–10 wks up to 1,500 m² and 10–12 above (was 10–14); client gateways GW / GW3 1 wk for 150–1,500 m² (was 2); programme float PROG-FLOAT +1 wk per 26 (was 13); new design rows DS2/DS3/DS4-DM and -EW for demolition and external works only; construction CN3 industrial S4–S6 18–28 / 24–34 / 30–44 (was 22–36 / 32–52 / 48–72), CN1 S6 50–70 (was 60–84), CF1 S4 10–14 (was 12–20), CX1 single-storey extension S1–S4 10–14 / 14–20 / 18–24 / 22–30 (was 7–10 / 8–12 / 12–18 / 18–26), CX2 S2–S3 16–22 / 20–28 (was 12–18 / 18–26) so multi-storey stays above single-storey.</t>
+  </si>
+  <si>
+    <t>BLK-1</t>
+  </si>
+  <si>
+    <t>During school term time</t>
+  </si>
+  <si>
+    <t>Construction blackout</t>
+  </si>
+  <si>
+    <t>BLACKOUT</t>
+  </si>
+  <si>
+    <t>01-04/02-12; 02-22/03-28; 04-13/05-22; 06-01/07-21; 09-02/10-23; 11-02/12-19</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>School terms in England (the gaps between the HOL-1...HOL-6 holidays). Work on site stops in term and runs in the holidays.</t>
+  </si>
+  <si>
+    <t>BLK-2</t>
+  </si>
+  <si>
+    <t>During university term time</t>
+  </si>
+  <si>
+    <t>09-29/12-12; 01-05/03-20; 04-20/06-19</t>
+  </si>
+  <si>
+    <t>Education; Student accommodation (PBSA / halls)</t>
+  </si>
+  <si>
+    <t>Typical three-term UK university year, exams included in the summer term.</t>
+  </si>
+  <si>
+    <t>BLK-3</t>
+  </si>
+  <si>
+    <t>During Christmas trading (November–mid-January)</t>
+  </si>
+  <si>
+    <t>11-01/01-15</t>
+  </si>
+  <si>
+    <t>Retail; Hospitality / leisure; Mixed use</t>
+  </si>
+  <si>
+    <t>Peak trading embargo common in retail and hospitality leases.</t>
+  </si>
+  <si>
+    <t>BLK-4</t>
+  </si>
+  <si>
+    <t>During winter pressures (December–March)</t>
+  </si>
+  <si>
+    <t>12-01/03-31</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>NHS winter pressures: estates works on live clinical areas are usually paused.</t>
+  </si>
+  <si>
+    <t>v4.9  ·  October 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t>v4.9</t>
+  </si>
+  <si>
+    <t>Construction blackouts (Q4.2a/Q4.2b, 11 Oct 2026): Modifiers rows BLK-1...BLK-4 are the periods a user can tick when work on site cannot take place. Modifier = the wording shown; Value = blocked periods, MM-DD/MM-DD separated by ';' (a range may cross the new year), repeated every year; Trigger = the Q1.3 building uses that see the option (';'). The user can also enter up to three specific date ranges. Construction is fitted around every ticked period. Add an option by adding a BLK row.</t>
   </si>
 </sst>
 </file>
@@ -2052,7 +2124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2070,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2397,10 +2469,18 @@
     </row>
     <row r="47" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>526</v>
+    </row>
+    <row r="48" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -5720,7 +5800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6214,98 +6294,104 @@
         <v>438</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>457</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>474</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>458</v>
@@ -6314,19 +6400,21 @@
         <v>459</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G26" s="6"/>
+        <v>461</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>458</v>
@@ -6335,19 +6423,19 @@
         <v>459</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>466</v>
       </c>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>458</v>
@@ -6356,107 +6444,105 @@
         <v>459</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>488</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>485</v>
@@ -6465,19 +6551,21 @@
         <v>486</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="G33" s="6"/>
+        <v>457</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>485</v>
@@ -6486,19 +6574,19 @@
         <v>486</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>485</v>
@@ -6507,12 +6595,96 @@
         <v>486</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E39" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="G35" s="6"/>
+      <c r="G39" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514338E3-E2D9-43A9-9CEA-1DBD5BB77AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8D549F-5038-43EE-9AFB-2B8C33C7EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,15 +17,16 @@
     <sheet name="Durations" sheetId="2" r:id="rId2"/>
     <sheet name="Construction" sheetId="3" r:id="rId3"/>
     <sheet name="Modifiers" sheetId="4" r:id="rId4"/>
-    <sheet name="FastTrack" sheetId="5" r:id="rId5"/>
-    <sheet name="Assumptions" sheetId="6" r:id="rId6"/>
+    <sheet name="Restrictions" sheetId="7" r:id="rId5"/>
+    <sheet name="FastTrack" sheetId="5" r:id="rId6"/>
+    <sheet name="Assumptions" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="600">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -1608,86 +1609,233 @@
     <t>Durations shortened after test batch 4 (11 Oct 2026, 30 scenarios): formal tender TN1 8–10 wks up to 1,500 m² and 10–12 above (was 10–14); client gateways GW / GW3 1 wk for 150–1,500 m² (was 2); programme float PROG-FLOAT +1 wk per 26 (was 13); new design rows DS2/DS3/DS4-DM and -EW for demolition and external works only; construction CN3 industrial S4–S6 18–28 / 24–34 / 30–44 (was 22–36 / 32–52 / 48–72), CN1 S6 50–70 (was 60–84), CF1 S4 10–14 (was 12–20), CX1 single-storey extension S1–S4 10–14 / 14–20 / 18–24 / 22–30 (was 7–10 / 8–12 / 12–18 / 18–26), CX2 S2–S3 16–22 / 20–28 (was 12–18 / 18–26) so multi-storey stays above single-storey.</t>
   </si>
   <si>
-    <t>BLK-1</t>
-  </si>
-  <si>
-    <t>During school term time</t>
-  </si>
-  <si>
-    <t>Construction blackout</t>
-  </si>
-  <si>
-    <t>BLACKOUT</t>
-  </si>
-  <si>
     <t>01-04/02-12; 02-22/03-28; 04-13/05-22; 06-01/07-21; 09-02/10-23; 11-02/12-19</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>School terms in England (the gaps between the HOL-1...HOL-6 holidays). Work on site stops in term and runs in the holidays.</t>
-  </si>
-  <si>
-    <t>BLK-2</t>
-  </si>
-  <si>
-    <t>During university term time</t>
-  </si>
-  <si>
-    <t>09-29/12-12; 01-05/03-20; 04-20/06-19</t>
-  </si>
-  <si>
     <t>Education; Student accommodation (PBSA / halls)</t>
   </si>
   <si>
-    <t>Typical three-term UK university year, exams included in the summer term.</t>
-  </si>
-  <si>
-    <t>BLK-3</t>
-  </si>
-  <si>
-    <t>During Christmas trading (November–mid-January)</t>
-  </si>
-  <si>
-    <t>11-01/01-15</t>
-  </si>
-  <si>
-    <t>Retail; Hospitality / leisure; Mixed use</t>
-  </si>
-  <si>
-    <t>Peak trading embargo common in retail and hospitality leases.</t>
-  </si>
-  <si>
-    <t>BLK-4</t>
-  </si>
-  <si>
-    <t>During winter pressures (December–March)</t>
-  </si>
-  <si>
     <t>12-01/03-31</t>
   </si>
   <si>
     <t>Healthcare</t>
   </si>
   <si>
-    <t>NHS winter pressures: estates works on live clinical areas are usually paused.</t>
-  </si>
-  <si>
     <t>v4.9  ·  October 2026  ·  Nabil Kayali</t>
   </si>
   <si>
     <t>v4.9</t>
   </si>
   <si>
-    <t>Construction blackouts (Q4.2a/Q4.2b, 11 Oct 2026): Modifiers rows BLK-1...BLK-4 are the periods a user can tick when work on site cannot take place. Modifier = the wording shown; Value = blocked periods, MM-DD/MM-DD separated by ';' (a range may cross the new year), repeated every year; Trigger = the Q1.3 building uses that see the option (';'). The user can also enter up to three specific date ranges. Construction is fitted around every ticked period. Add an option by adding a BLK row.</t>
+    <t>SITE WORK RESTRICTIONS — periods when work on site is not permitted (Q4.2b). One row per option; the user sees "Restriction (Dates shown)" for their building use and may tick several. Blocked periods repeat every year.</t>
+  </si>
+  <si>
+    <t>Building uses</t>
+  </si>
+  <si>
+    <t>Restriction</t>
+  </si>
+  <si>
+    <t>Dates shown</t>
+  </si>
+  <si>
+    <t>Blocked periods</t>
+  </si>
+  <si>
+    <t>R-01</t>
+  </si>
+  <si>
+    <t>School term time</t>
+  </si>
+  <si>
+    <t>Sep–Jul; work in school holidays</t>
+  </si>
+  <si>
+    <t>England school terms: the gaps between the six holidays (HOL-1...HOL-6 on Modifiers).</t>
+  </si>
+  <si>
+    <t>R-02</t>
+  </si>
+  <si>
+    <t>School exams</t>
+  </si>
+  <si>
+    <t>mid May – end Jun</t>
+  </si>
+  <si>
+    <t>05-11/06-30</t>
+  </si>
+  <si>
+    <t>GCSE and A level written exams.</t>
+  </si>
+  <si>
+    <t>R-03</t>
+  </si>
+  <si>
+    <t>University term time</t>
+  </si>
+  <si>
+    <t>late Sep – mid Jun; work in vacations</t>
+  </si>
+  <si>
+    <t>09-29/12-12; 01-05/03-20; 04-20/06-12</t>
+  </si>
+  <si>
+    <t>Typical three-term UK university year.</t>
+  </si>
+  <si>
+    <t>R-04</t>
+  </si>
+  <si>
+    <t>University exams</t>
+  </si>
+  <si>
+    <t>May – mid Jun</t>
+  </si>
+  <si>
+    <t>05-01/06-14</t>
+  </si>
+  <si>
+    <t>Main summer exam period.</t>
+  </si>
+  <si>
+    <t>R-05</t>
+  </si>
+  <si>
+    <t>Graduation</t>
+  </si>
+  <si>
+    <t>mid – late Jul</t>
+  </si>
+  <si>
+    <t>07-10/07-25</t>
+  </si>
+  <si>
+    <t>Degree ceremonies.</t>
+  </si>
+  <si>
+    <t>R-06</t>
+  </si>
+  <si>
+    <t>Student arrivals</t>
+  </si>
+  <si>
+    <t>mid – end Sep</t>
+  </si>
+  <si>
+    <t>09-14/09-30</t>
+  </si>
+  <si>
+    <t>Move-in and welcome week.</t>
+  </si>
+  <si>
+    <t>R-07</t>
+  </si>
+  <si>
+    <t>Winter pressures</t>
+  </si>
+  <si>
+    <t>Dec – Mar</t>
+  </si>
+  <si>
+    <t>NHS winter: works in live clinical areas usually paused.</t>
+  </si>
+  <si>
+    <t>R-08</t>
+  </si>
+  <si>
+    <t>Healthcare; Hospitality / leisure; Residential</t>
+  </si>
+  <si>
+    <t>Christmas and New Year</t>
+  </si>
+  <si>
+    <t>15 Dec – 5 Jan</t>
+  </si>
+  <si>
+    <t>12-15/01-05</t>
+  </si>
+  <si>
+    <t>Occupied homes, hotels, wards.</t>
+  </si>
+  <si>
+    <t>R-09</t>
+  </si>
+  <si>
+    <t>Retail; Mixed use</t>
+  </si>
+  <si>
+    <t>Christmas trading</t>
+  </si>
+  <si>
+    <t>Peak trading embargo common in retail leases.</t>
+  </si>
+  <si>
+    <t>R-10</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Black Friday peak</t>
+  </si>
+  <si>
+    <t>20 – 30 Nov</t>
+  </si>
+  <si>
+    <t>11-20/11-30</t>
+  </si>
+  <si>
+    <t>Pre-Christmas sales peak.</t>
+  </si>
+  <si>
+    <t>R-11</t>
+  </si>
+  <si>
+    <t>Hospitality / leisure</t>
+  </si>
+  <si>
+    <t>Summer season</t>
+  </si>
+  <si>
+    <t>Jul – Aug</t>
+  </si>
+  <si>
+    <t>07-01/08-31</t>
+  </si>
+  <si>
+    <t>Peak visitor season.</t>
+  </si>
+  <si>
+    <t>R-12</t>
+  </si>
+  <si>
+    <t>Industrial / warehouse</t>
+  </si>
+  <si>
+    <t>Peak distribution season</t>
+  </si>
+  <si>
+    <t>Oct – Dec</t>
+  </si>
+  <si>
+    <t>10-01/12-31</t>
+  </si>
+  <si>
+    <t>Pre-Christmas logistics peak.</t>
+  </si>
+  <si>
+    <t>Site work restrictions (Q4.2a / Q4.2b, 11 Oct 2026): new sheet 'Restrictions' lists the periods a user can tick when work on site is not permitted, by building use (Education 6, Healthcare 2, Retail 3, Hospitality 2, Residential 1, Student accommodation 2, Industrial 1, Mixed use 1). Columns: ID, Building uses (Q1.3 labels, ';'), Restriction and Dates shown (what the user reads), Blocked periods (MM-DD/MM-DD, ';', repeated every year; a period may cross the new year), Notes. The user can also enter up to three specific date ranges. Construction is fitted around every ticked period. Add or change an option here; no code change.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1721,8 +1869,22 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1739,6 +1901,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF0F7"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A2E4A"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1806,7 +1974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1859,6 +2027,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2142,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2477,10 +2650,10 @@
     </row>
     <row r="48" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>550</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -5800,7 +5973,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6294,104 +6467,98 @@
         <v>438</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>526</v>
+        <v>456</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>527</v>
+        <v>457</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>528</v>
+        <v>458</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>530</v>
+        <v>460</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>531</v>
+        <v>461</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>533</v>
+        <v>463</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>534</v>
+        <v>464</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>528</v>
+        <v>458</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>535</v>
+        <v>465</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>538</v>
+        <v>467</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>539</v>
+        <v>468</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>528</v>
+        <v>458</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>540</v>
+        <v>469</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>543</v>
+        <v>470</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>544</v>
+        <v>471</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>528</v>
+        <v>458</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>545</v>
+        <v>472</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>458</v>
@@ -6400,21 +6567,19 @@
         <v>459</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>462</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>458</v>
@@ -6423,19 +6588,19 @@
         <v>459</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>466</v>
       </c>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>458</v>
@@ -6444,105 +6609,107 @@
         <v>459</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G28" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G29" s="6"/>
+        <v>457</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>485</v>
@@ -6551,21 +6718,19 @@
         <v>486</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>488</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>485</v>
@@ -6574,19 +6739,19 @@
         <v>486</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>485</v>
@@ -6595,96 +6760,12 @@
         <v>486</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="G39" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6693,6 +6774,289 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{839EDCC2-71D0-462A-8812-A8D501EB7B8A}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="60.7109375" customWidth="1"/>
+    <col min="6" max="6" width="50.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>534</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>536</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>528</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>549</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>550</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>552</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>560</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>562</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>528</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>564</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>569</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>598</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6931,7 +7295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8D549F-5038-43EE-9AFB-2B8C33C7EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB5A6E9-E8C2-43C7-A44C-EE0134690F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="608">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -1624,9 +1624,6 @@
     <t>Healthcare</t>
   </si>
   <si>
-    <t>v4.9  ·  October 2026  ·  Nabil Kayali</t>
-  </si>
-  <si>
     <t>v4.9</t>
   </si>
   <si>
@@ -1829,6 +1826,33 @@
   </si>
   <si>
     <t>Site work restrictions (Q4.2a / Q4.2b, 11 Oct 2026): new sheet 'Restrictions' lists the periods a user can tick when work on site is not permitted, by building use (Education 6, Healthcare 2, Retail 3, Hospitality 2, Residential 1, Student accommodation 2, Industrial 1, Mixed use 1). Columns: ID, Building uses (Q1.3 labels, ';'), Restriction and Dates shown (what the user reads), Blocked periods (MM-DD/MM-DD, ';', repeated every year; a period may cross the new year), Notes. The user can also enter up to three specific date ranges. Construction is fitted around every ticked period. Add or change an option here; no code change.</t>
+  </si>
+  <si>
+    <t>ME-HEAVY</t>
+  </si>
+  <si>
+    <t>M&amp;E-heavy design uplift threshold</t>
+  </si>
+  <si>
+    <t>Stage 3 / Stage 4 design</t>
+  </si>
+  <si>
+    <t>THRESHOLD</t>
+  </si>
+  <si>
+    <t>Number of services (Group 5) items in Q2.3 at or above which DS3a and DS4a are added</t>
+  </si>
+  <si>
+    <t>Moved from the code (v4.10). DS3a / DS4a are now 1–2 weeks, so the threshold matters less.</t>
+  </si>
+  <si>
+    <t>v4.10  ·  October 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t>v4.10</t>
+  </si>
+  <si>
+    <t>Duration review against the owner's projects (11 Oct 2026). Occupation uplift OCC-1 +15% (was 30%), OCC-2 +10% (was 20%): Lakeside occupied ran about 10% slower than vacant Riley Court; Claycroft now 73 weeks against 74 planned. Design uplifts DS3a 1 week, DS4a 1 up to 500 m² and 2 above (were up to 3 and 4; they fired on almost every project). Planning PL1 / PL4 8–10 up to 1,500 m² (minor, 8-week statutory) and 10–13 above (major); PL2 8–10 up to 1,500 m². Tender TN1 S1–S3 4–6 / 5–7 / 6–8. Construction CF2 S5–S6 12–18 / 18–28, CF1 S5–S6 16–24 / 24–36, CN1 S5 40–56, CN2 S3–S6 26–38 / 36–52 / 50–70 / 70–95, CE1 S5–S6 8–12 / 10–16. New Modifiers row ME-HEAVY (4) holds the threshold the code used. Unchanged and confirmed: CR1 (Riley Court 41 vs 42), CD1 (Whitefields 14), CF2 S1–S4 (Co-op 8 vs 7, IBRB 3), CH1.</t>
   </si>
 </sst>
 </file>
@@ -2006,6 +2030,11 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2027,11 +2056,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2297,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2305,17 +2329,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>531</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2650,10 +2674,18 @@
     </row>
     <row r="48" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -2747,29 +2779,29 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="15"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="18"/>
     </row>
     <row r="3" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -3162,29 +3194,29 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="15"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="18"/>
     </row>
     <row r="10" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -3463,34 +3495,34 @@
         <v>1</v>
       </c>
       <c r="F14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M14" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N14" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P14" s="7" t="s">
         <v>80</v>
@@ -3658,34 +3690,34 @@
         <v>1</v>
       </c>
       <c r="F17" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M17" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N17" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O17" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" s="7" t="s">
         <v>80</v>
@@ -4097,29 +4129,29 @@
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="15"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="18"/>
     </row>
     <row r="25" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
@@ -4252,29 +4284,29 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="15"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="18"/>
     </row>
     <row r="28" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
@@ -4290,34 +4322,34 @@
         <v>8</v>
       </c>
       <c r="E28" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F28" s="7">
         <v>8</v>
       </c>
       <c r="G28" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H28" s="7">
         <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J28" s="7">
         <v>8</v>
       </c>
       <c r="K28" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L28" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M28" s="7">
         <v>13</v>
       </c>
       <c r="N28" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O28" s="7">
         <v>13</v>
@@ -4355,25 +4387,25 @@
         <v>8</v>
       </c>
       <c r="E29" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F29" s="7">
         <v>8</v>
       </c>
       <c r="G29" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H29" s="7">
         <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J29" s="7">
         <v>8</v>
       </c>
       <c r="K29" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L29" s="7">
         <v>8</v>
@@ -4485,34 +4517,34 @@
         <v>8</v>
       </c>
       <c r="E31" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F31" s="7">
         <v>8</v>
       </c>
       <c r="G31" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H31" s="7">
         <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J31" s="7">
         <v>8</v>
       </c>
       <c r="K31" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L31" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M31" s="7">
         <v>13</v>
       </c>
       <c r="N31" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O31" s="7">
         <v>13</v>
@@ -4667,29 +4699,29 @@
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="18"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="21"/>
     </row>
     <row r="35" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
@@ -4822,29 +4854,29 @@
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="15"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="18"/>
     </row>
     <row r="38" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
@@ -4857,22 +4889,22 @@
         <v>197</v>
       </c>
       <c r="D38" s="7">
+        <v>4</v>
+      </c>
+      <c r="E38" s="7">
         <v>6</v>
       </c>
-      <c r="E38" s="7">
+      <c r="F38" s="7">
+        <v>5</v>
+      </c>
+      <c r="G38" s="7">
+        <v>7</v>
+      </c>
+      <c r="H38" s="7">
+        <v>6</v>
+      </c>
+      <c r="I38" s="7">
         <v>8</v>
-      </c>
-      <c r="F38" s="7">
-        <v>8</v>
-      </c>
-      <c r="G38" s="7">
-        <v>10</v>
-      </c>
-      <c r="H38" s="7">
-        <v>8</v>
-      </c>
-      <c r="I38" s="7">
-        <v>10</v>
       </c>
       <c r="J38" s="7">
         <v>8</v>
@@ -5349,10 +5381,10 @@
         <v>48</v>
       </c>
       <c r="K2" s="7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L2" s="7">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="M2" s="7">
         <v>50</v>
@@ -5387,28 +5419,28 @@
         <v>32</v>
       </c>
       <c r="G3" s="7">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H3" s="7">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I3" s="7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J3" s="7">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="K3" s="7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L3" s="7">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="M3" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N3" s="7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>80</v>
@@ -5697,16 +5729,16 @@
         <v>14</v>
       </c>
       <c r="K9" s="7">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L9" s="7">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M9" s="7">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N9" s="7">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>80</v>
@@ -5747,16 +5779,16 @@
         <v>9</v>
       </c>
       <c r="K10" s="7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L10" s="7">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M10" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N10" s="7">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Q10" s="7" t="s">
         <v>80</v>
@@ -5847,16 +5879,16 @@
         <v>10</v>
       </c>
       <c r="K12" s="7">
+        <v>8</v>
+      </c>
+      <c r="L12" s="7">
+        <v>12</v>
+      </c>
+      <c r="M12" s="7">
         <v>10</v>
       </c>
-      <c r="L12" s="7">
+      <c r="N12" s="7">
         <v>16</v>
-      </c>
-      <c r="M12" s="7">
-        <v>14</v>
-      </c>
-      <c r="N12" s="7">
-        <v>22</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>80</v>
@@ -5973,7 +6005,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6136,7 +6168,7 @@
         <v>275</v>
       </c>
       <c r="E7" s="6">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>276</v>
@@ -6159,7 +6191,7 @@
         <v>275</v>
       </c>
       <c r="E8" s="6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>279</v>
@@ -6193,102 +6225,102 @@
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="E10" s="6">
+        <v>4</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B11" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E11" s="6">
         <v>0.15</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>424</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B13" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E13" s="6">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F13" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>300</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>301</v>
-      </c>
-      <c r="C13" t="s">
-        <v>274</v>
-      </c>
-      <c r="D13" t="s">
-        <v>275</v>
-      </c>
-      <c r="E13">
-        <v>0.1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>429</v>
-      </c>
-      <c r="G13" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>303</v>
-      </c>
-      <c r="B14" t="s">
-        <v>304</v>
       </c>
       <c r="C14" t="s">
         <v>274</v>
@@ -6297,67 +6329,67 @@
         <v>275</v>
       </c>
       <c r="E14">
+        <v>0.1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>429</v>
+      </c>
+      <c r="G14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E15">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>430</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G15" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="16" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>310</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>434</v>
@@ -6366,7 +6398,7 @@
         <v>435</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>437</v>
@@ -6377,10 +6409,10 @@
     </row>
     <row r="18" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>434</v>
@@ -6389,7 +6421,7 @@
         <v>435</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>437</v>
@@ -6400,10 +6432,10 @@
     </row>
     <row r="19" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>434</v>
@@ -6412,7 +6444,7 @@
         <v>435</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>437</v>
@@ -6423,10 +6455,10 @@
     </row>
     <row r="20" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>434</v>
@@ -6435,7 +6467,7 @@
         <v>435</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>437</v>
@@ -6446,10 +6478,10 @@
     </row>
     <row r="21" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>434</v>
@@ -6458,7 +6490,7 @@
         <v>435</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>437</v>
@@ -6467,35 +6499,35 @@
         <v>438</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="48" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B23" s="6" t="s">
         <v>457</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>464</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>458</v>
@@ -6504,19 +6536,21 @@
         <v>459</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G23" s="6"/>
+        <v>461</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>458</v>
@@ -6525,7 +6559,7 @@
         <v>459</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>466</v>
@@ -6534,10 +6568,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>458</v>
@@ -6546,7 +6580,7 @@
         <v>459</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>466</v>
@@ -6555,10 +6589,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>458</v>
@@ -6567,7 +6601,7 @@
         <v>459</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>466</v>
@@ -6576,10 +6610,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>458</v>
@@ -6588,19 +6622,19 @@
         <v>459</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>466</v>
       </c>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>458</v>
@@ -6609,44 +6643,42 @@
         <v>459</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+    <row r="30" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="6" t="s">
         <v>484</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>487</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>490</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>485</v>
@@ -6655,19 +6687,21 @@
         <v>486</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="G30" s="6"/>
+        <v>457</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>485</v>
@@ -6676,19 +6710,19 @@
         <v>486</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>485</v>
@@ -6697,19 +6731,19 @@
         <v>486</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>485</v>
@@ -6718,19 +6752,19 @@
         <v>486</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>485</v>
@@ -6739,19 +6773,19 @@
         <v>486</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>485</v>
@@ -6760,12 +6794,33 @@
         <v>486</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E36" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="G35" s="6"/>
+      <c r="G36" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6787,268 +6842,268 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="11" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="E3" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="F3" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>537</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="B4" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="D4" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>539</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>540</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>526</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="C5" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="D5" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="C5" s="21" t="s">
-        <v>543</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>544</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>545</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>547</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="C7" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>548</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>549</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>550</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>552</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>553</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>555</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>557</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>558</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>559</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>560</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="C9" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>528</v>
-      </c>
-      <c r="C9" s="21" t="s">
+      <c r="D9" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="E9" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="F9" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="F9" s="21" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="B10" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>567</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="C10" s="21" t="s">
+      <c r="D10" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="E10" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>569</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="F10" s="21" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="B11" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="C11" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="D11" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="E11" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F11" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="F11" s="21" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="B12" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="C12" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="D12" s="13" t="s">
+        <v>573</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>579</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>574</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>575</v>
-      </c>
-      <c r="F12" s="21" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="B13" s="13" t="s">
         <v>581</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="C13" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="D13" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="E13" s="13" t="s">
         <v>584</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="F13" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="F13" s="21" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="B14" s="13" t="s">
         <v>587</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="C14" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="D14" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="E14" s="13" t="s">
         <v>590</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="F14" s="13" t="s">
         <v>591</v>
       </c>
-      <c r="F14" s="21" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="B15" s="13" t="s">
         <v>593</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="C15" s="13" t="s">
         <v>594</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="D15" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="F15" s="13" t="s">
         <v>597</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB5A6E9-E8C2-43C7-A44C-EE0134690F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB142D3B-13B6-4D6B-A020-388DED8CE785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,16 @@
     <sheet name="Construction" sheetId="3" r:id="rId3"/>
     <sheet name="Modifiers" sheetId="4" r:id="rId4"/>
     <sheet name="Restrictions" sheetId="7" r:id="rId5"/>
-    <sheet name="FastTrack" sheetId="5" r:id="rId6"/>
-    <sheet name="Assumptions" sheetId="6" r:id="rId7"/>
+    <sheet name="Procurement" sheetId="8" r:id="rId6"/>
+    <sheet name="FastTrack" sheetId="5" r:id="rId7"/>
+    <sheet name="Assumptions" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="654">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -1846,13 +1847,151 @@
     <t>Moved from the code (v4.10). DS3a / DS4a are now 1–2 weeks, so the threshold matters less.</t>
   </si>
   <si>
-    <t>v4.10  ·  October 2026  ·  Nabil Kayali</t>
-  </si>
-  <si>
     <t>v4.10</t>
   </si>
   <si>
     <t>Duration review against the owner's projects (11 Oct 2026). Occupation uplift OCC-1 +15% (was 30%), OCC-2 +10% (was 20%): Lakeside occupied ran about 10% slower than vacant Riley Court; Claycroft now 73 weeks against 74 planned. Design uplifts DS3a 1 week, DS4a 1 up to 500 m² and 2 above (were up to 3 and 4; they fired on almost every project). Planning PL1 / PL4 8–10 up to 1,500 m² (minor, 8-week statutory) and 10–13 above (major); PL2 8–10 up to 1,500 m². Tender TN1 S1–S3 4–6 / 5–7 / 6–8. Construction CF2 S5–S6 12–18 / 18–28, CF1 S5–S6 16–24 / 24–36, CN1 S5 40–56, CN2 S3–S6 26–38 / 36–52 / 50–70 / 70–95, CE1 S5–S6 8–12 / 10–16. New Modifiers row ME-HEAVY (4) holds the threshold the code used. Unchanged and confirmed: CR1 (Riley Court 41 vs 42), CD1 (Whitefields 14), CF2 S1–S4 (Co-op 8 vs 7, IBRB 3), CH1.</t>
+  </si>
+  <si>
+    <t>TN5</t>
+  </si>
+  <si>
+    <t>Tender — Framework direct award</t>
+  </si>
+  <si>
+    <t>Route to market = Framework direct award</t>
+  </si>
+  <si>
+    <t>v4.11: shorter than a mini-competition (TN3).</t>
+  </si>
+  <si>
+    <t>TN7</t>
+  </si>
+  <si>
+    <t>Second-stage price — Design &amp; Build 2 Stage</t>
+  </si>
+  <si>
+    <t>Route = Design &amp; Build 2 Stage (Procurement sheet)</t>
+  </si>
+  <si>
+    <t>v4.11: contractor prices the developed design at the end of Stage 3 (RIBA Plan of Work 2020).</t>
+  </si>
+  <si>
+    <t>DS34-MW</t>
+  </si>
+  <si>
+    <t>Stages 3–4 — Design and specification (minor works)</t>
+  </si>
+  <si>
+    <t>Contract = Minor Works (Procurement sheet)</t>
+  </si>
+  <si>
+    <t>v4.11: replaces Stage 3 and Stage 4 on a Minor Works / MWD / ECS contract.</t>
+  </si>
+  <si>
+    <t>PROCUREMENT ROUTES AND THE PROGRAMME — RIBA Plan of Work 2020. The route (from the Procurement Reference, matched by ID) sets when the contractor is brought in and who does Stage 4; the route to market sets the tender length (TN rows); the contract can change the design time (table below). No overlap: work on site starts only when Stage 4 is complete (owner, 11 Oct 2026).</t>
+  </si>
+  <si>
+    <t>Route</t>
+  </si>
+  <si>
+    <t>Contractor brought in after</t>
+  </si>
+  <si>
+    <t>Stage 4 by</t>
+  </si>
+  <si>
+    <t>First tender runs alongside</t>
+  </si>
+  <si>
+    <t>Second-stage price row</t>
+  </si>
+  <si>
+    <t>PR1</t>
+  </si>
+  <si>
+    <t>Traditional</t>
+  </si>
+  <si>
+    <t>Stage 4</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Tender at the end of Stage 4.</t>
+  </si>
+  <si>
+    <t>PR2</t>
+  </si>
+  <si>
+    <t>Design &amp; Build 1 Stage</t>
+  </si>
+  <si>
+    <t>Stage 3</t>
+  </si>
+  <si>
+    <t>Contractor</t>
+  </si>
+  <si>
+    <t>Employer's Requirements at the end of Stage 3; contractor designs Stage 4 after award.</t>
+  </si>
+  <si>
+    <t>PR3</t>
+  </si>
+  <si>
+    <t>Design &amp; Build 2 Stage</t>
+  </si>
+  <si>
+    <t>Stage 2</t>
+  </si>
+  <si>
+    <t>First-stage tender after Stage 2 runs alongside Stage 3 (PCSA); second-stage price at the end of Stage 3; contractor designs Stage 4.</t>
+  </si>
+  <si>
+    <t>PR4</t>
+  </si>
+  <si>
+    <t>Management Contract / Construction Management</t>
+  </si>
+  <si>
+    <t>Contractor appointed alongside Stage 3; trade packages let during Stage 4.</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Contracts</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>Stage 3 and Stage 4 replaced by one design-and-specification stage (Durations row)</t>
+  </si>
+  <si>
+    <t>JCT MW, JCT MWD, NEC4 ECS</t>
+  </si>
+  <si>
+    <t>CDP</t>
+  </si>
+  <si>
+    <t>Client's Stage 4 as a share of the normal Stage 4</t>
+  </si>
+  <si>
+    <t>JCT ICD, JCT SBC + CDP</t>
+  </si>
+  <si>
+    <t>v4.11  ·  October 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t>v4.11</t>
+  </si>
+  <si>
+    <t>Procurement routes follow the RIBA Plan of Work 2020 (11 Oct 2026). New sheet 'Procurement': for each route (PR1 Traditional, PR2 Design &amp; Build 1 Stage, PR3 Design &amp; Build 2 Stage, PR4 Management Contract / Construction Management, matched to the Procurement Reference by ID) the stage after which the contractor is brought in, who does Stage 4, whether the first tender runs alongside Stage 3, and the second-stage price row; and the contract effects (MW: Stages 3–4 replaced by DS34-MW; CDP: client's Stage 4 x 0.8). No overlap of Stage 4 and construction. New Durations rows TN5 (framework direct award), TN7 (second-stage price) and DS34-MW (minor works design and specification).</t>
   </si>
 </sst>
 </file>
@@ -1998,7 +2137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2056,6 +2195,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2321,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2339,7 +2482,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>605</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2682,10 +2825,18 @@
     </row>
     <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>607</v>
+    </row>
+    <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -2699,7 +2850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -4128,117 +4279,117 @@
         <v>512</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2</v>
+      </c>
+      <c r="F24" s="7">
+        <v>2</v>
+      </c>
+      <c r="G24" s="7">
+        <v>3</v>
+      </c>
+      <c r="H24" s="7">
+        <v>2</v>
+      </c>
+      <c r="I24" s="7">
+        <v>4</v>
+      </c>
+      <c r="J24" s="7">
+        <v>3</v>
+      </c>
+      <c r="K24" s="7">
+        <v>5</v>
+      </c>
+      <c r="L24" s="7">
+        <v>3</v>
+      </c>
+      <c r="M24" s="7">
+        <v>5</v>
+      </c>
+      <c r="N24" s="7">
+        <v>3</v>
+      </c>
+      <c r="O24" s="7">
+        <v>5</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S24" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="T24" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="U24" s="7" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="18"/>
-    </row>
-    <row r="25" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1</v>
-      </c>
-      <c r="F25" s="7">
-        <v>1</v>
-      </c>
-      <c r="G25" s="7">
-        <v>1</v>
-      </c>
-      <c r="H25" s="7">
-        <v>1</v>
-      </c>
-      <c r="I25" s="7">
-        <v>1</v>
-      </c>
-      <c r="J25" s="7">
-        <v>1</v>
-      </c>
-      <c r="K25" s="7">
-        <v>1</v>
-      </c>
-      <c r="L25" s="7">
-        <v>2</v>
-      </c>
-      <c r="M25" s="7">
-        <v>2</v>
-      </c>
-      <c r="N25" s="7">
-        <v>2</v>
-      </c>
-      <c r="O25" s="7">
-        <v>2</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T25" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="U25" s="7" t="s">
-        <v>149</v>
-      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="18"/>
     </row>
     <row r="26" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>145</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="7">
         <v>1</v>
@@ -4277,111 +4428,111 @@
         <v>83</v>
       </c>
       <c r="T26" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="7">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>1</v>
+      </c>
+      <c r="I27" s="7">
+        <v>1</v>
+      </c>
+      <c r="J27" s="7">
+        <v>1</v>
+      </c>
+      <c r="K27" s="7">
+        <v>1</v>
+      </c>
+      <c r="L27" s="7">
+        <v>2</v>
+      </c>
+      <c r="M27" s="7">
+        <v>2</v>
+      </c>
+      <c r="N27" s="7">
+        <v>2</v>
+      </c>
+      <c r="O27" s="7">
+        <v>2</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T27" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="U26" s="7" t="s">
+      <c r="U27" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="18"/>
-    </row>
-    <row r="28" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D28" s="7">
-        <v>8</v>
-      </c>
-      <c r="E28" s="7">
-        <v>10</v>
-      </c>
-      <c r="F28" s="7">
-        <v>8</v>
-      </c>
-      <c r="G28" s="7">
-        <v>10</v>
-      </c>
-      <c r="H28" s="7">
-        <v>8</v>
-      </c>
-      <c r="I28" s="7">
-        <v>10</v>
-      </c>
-      <c r="J28" s="7">
-        <v>8</v>
-      </c>
-      <c r="K28" s="7">
-        <v>10</v>
-      </c>
-      <c r="L28" s="7">
-        <v>10</v>
-      </c>
-      <c r="M28" s="7">
-        <v>13</v>
-      </c>
-      <c r="N28" s="7">
-        <v>10</v>
-      </c>
-      <c r="O28" s="7">
-        <v>13</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R28" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S28" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T28" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="U28" s="7" t="s">
-        <v>161</v>
-      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="18"/>
     </row>
     <row r="29" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>156</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D29" s="7">
         <v>8</v>
@@ -4408,13 +4559,13 @@
         <v>10</v>
       </c>
       <c r="L29" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M29" s="7">
         <v>13</v>
       </c>
       <c r="N29" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O29" s="7">
         <v>13</v>
@@ -4432,57 +4583,57 @@
         <v>83</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="U29" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>156</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D30" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E30" s="7">
+        <v>10</v>
+      </c>
+      <c r="F30" s="7">
         <v>8</v>
       </c>
-      <c r="F30" s="7">
-        <v>4</v>
-      </c>
       <c r="G30" s="7">
+        <v>10</v>
+      </c>
+      <c r="H30" s="7">
         <v>8</v>
       </c>
-      <c r="H30" s="7">
-        <v>4</v>
-      </c>
       <c r="I30" s="7">
+        <v>10</v>
+      </c>
+      <c r="J30" s="7">
         <v>8</v>
       </c>
-      <c r="J30" s="7">
-        <v>4</v>
-      </c>
       <c r="K30" s="7">
+        <v>10</v>
+      </c>
+      <c r="L30" s="7">
         <v>8</v>
       </c>
-      <c r="L30" s="7">
-        <v>4</v>
-      </c>
       <c r="M30" s="7">
+        <v>13</v>
+      </c>
+      <c r="N30" s="7">
         <v>8</v>
       </c>
-      <c r="N30" s="7">
-        <v>4</v>
-      </c>
       <c r="O30" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P30" s="7" t="s">
         <v>80</v>
@@ -4497,57 +4648,57 @@
         <v>83</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>156</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D31" s="7">
+        <v>4</v>
+      </c>
+      <c r="E31" s="7">
         <v>8</v>
       </c>
-      <c r="E31" s="7">
-        <v>10</v>
-      </c>
       <c r="F31" s="7">
+        <v>4</v>
+      </c>
+      <c r="G31" s="7">
         <v>8</v>
       </c>
-      <c r="G31" s="7">
-        <v>10</v>
-      </c>
       <c r="H31" s="7">
+        <v>4</v>
+      </c>
+      <c r="I31" s="7">
         <v>8</v>
       </c>
-      <c r="I31" s="7">
-        <v>10</v>
-      </c>
       <c r="J31" s="7">
+        <v>4</v>
+      </c>
+      <c r="K31" s="7">
         <v>8</v>
       </c>
-      <c r="K31" s="7">
-        <v>10</v>
-      </c>
       <c r="L31" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M31" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N31" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O31" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P31" s="7" t="s">
         <v>80</v>
@@ -4562,128 +4713,128 @@
         <v>83</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="U31" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>156</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D32" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E32" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F32" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G32" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H32" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K32" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L32" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M32" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N32" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O32" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P32" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="S32" s="7" t="s">
         <v>83</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="U32" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>156</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D33" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F33" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G33" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H33" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J33" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K33" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L33" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M33" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N33" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P33" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="R33" s="7" t="s">
         <v>112</v>
@@ -4692,147 +4843,147 @@
         <v>83</v>
       </c>
       <c r="T33" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <v>0</v>
+      </c>
+      <c r="M34" s="7">
+        <v>0</v>
+      </c>
+      <c r="N34" s="7">
+        <v>0</v>
+      </c>
+      <c r="O34" s="7">
+        <v>0</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="R34" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S34" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T34" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="U33" s="7" t="s">
+      <c r="U34" s="7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
-      <c r="U34" s="21"/>
-    </row>
-    <row r="35" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D35" s="7">
-        <v>2</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4</v>
-      </c>
-      <c r="F35" s="7">
-        <v>2</v>
-      </c>
-      <c r="G35" s="7">
-        <v>4</v>
-      </c>
-      <c r="H35" s="7">
-        <v>2</v>
-      </c>
-      <c r="I35" s="7">
-        <v>4</v>
-      </c>
-      <c r="J35" s="7">
-        <v>5</v>
-      </c>
-      <c r="K35" s="7">
-        <v>8</v>
-      </c>
-      <c r="L35" s="7">
-        <v>5</v>
-      </c>
-      <c r="M35" s="7">
-        <v>8</v>
-      </c>
-      <c r="N35" s="7">
-        <v>6</v>
-      </c>
-      <c r="O35" s="7">
-        <v>10</v>
-      </c>
-      <c r="P35" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q35" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="R35" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T35" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="U35" s="7" t="s">
-        <v>189</v>
-      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="21"/>
     </row>
     <row r="36" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>185</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D36" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="7">
+        <v>4</v>
+      </c>
+      <c r="F36" s="7">
+        <v>2</v>
+      </c>
+      <c r="G36" s="7">
+        <v>4</v>
+      </c>
+      <c r="H36" s="7">
+        <v>2</v>
+      </c>
+      <c r="I36" s="7">
+        <v>4</v>
+      </c>
+      <c r="J36" s="7">
         <v>5</v>
       </c>
-      <c r="F36" s="7">
-        <v>3</v>
-      </c>
-      <c r="G36" s="7">
+      <c r="K36" s="7">
+        <v>8</v>
+      </c>
+      <c r="L36" s="7">
         <v>5</v>
       </c>
-      <c r="H36" s="7">
-        <v>3</v>
-      </c>
-      <c r="I36" s="7">
-        <v>5</v>
-      </c>
-      <c r="J36" s="7">
-        <v>3</v>
-      </c>
-      <c r="K36" s="7">
-        <v>5</v>
-      </c>
-      <c r="L36" s="7">
-        <v>3</v>
-      </c>
       <c r="M36" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N36" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O36" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>80</v>
@@ -4847,147 +4998,147 @@
         <v>83</v>
       </c>
       <c r="T36" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" s="7">
+        <v>3</v>
+      </c>
+      <c r="E37" s="7">
+        <v>5</v>
+      </c>
+      <c r="F37" s="7">
+        <v>3</v>
+      </c>
+      <c r="G37" s="7">
+        <v>5</v>
+      </c>
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+      <c r="I37" s="7">
+        <v>5</v>
+      </c>
+      <c r="J37" s="7">
+        <v>3</v>
+      </c>
+      <c r="K37" s="7">
+        <v>5</v>
+      </c>
+      <c r="L37" s="7">
+        <v>3</v>
+      </c>
+      <c r="M37" s="7">
+        <v>5</v>
+      </c>
+      <c r="N37" s="7">
+        <v>3</v>
+      </c>
+      <c r="O37" s="7">
+        <v>5</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T37" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="U36" s="7" t="s">
+      <c r="U37" s="7" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="18"/>
-    </row>
-    <row r="38" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D38" s="7">
-        <v>4</v>
-      </c>
-      <c r="E38" s="7">
-        <v>6</v>
-      </c>
-      <c r="F38" s="7">
-        <v>5</v>
-      </c>
-      <c r="G38" s="7">
-        <v>7</v>
-      </c>
-      <c r="H38" s="7">
-        <v>6</v>
-      </c>
-      <c r="I38" s="7">
-        <v>8</v>
-      </c>
-      <c r="J38" s="7">
-        <v>8</v>
-      </c>
-      <c r="K38" s="7">
-        <v>10</v>
-      </c>
-      <c r="L38" s="7">
-        <v>10</v>
-      </c>
-      <c r="M38" s="7">
-        <v>12</v>
-      </c>
-      <c r="N38" s="7">
-        <v>10</v>
-      </c>
-      <c r="O38" s="7">
-        <v>12</v>
-      </c>
-      <c r="P38" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="R38" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="S38" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T38" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="U38" s="7" t="s">
-        <v>199</v>
-      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="18"/>
     </row>
     <row r="39" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>196</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D39" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F39" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G39" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I39" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J39" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K39" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L39" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M39" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N39" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O39" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P39" s="7" t="s">
         <v>80</v>
@@ -5002,21 +5153,21 @@
         <v>83</v>
       </c>
       <c r="T39" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>196</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D40" s="7">
         <v>3</v>
@@ -5025,16 +5176,16 @@
         <v>4</v>
       </c>
       <c r="F40" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40" s="7">
         <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" s="7">
         <v>4</v>
@@ -5067,57 +5218,57 @@
         <v>83</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="U40" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>425</v>
+        <v>204</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>196</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>426</v>
+        <v>205</v>
       </c>
       <c r="D41" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O41" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P41" s="7" t="s">
         <v>80</v>
@@ -5132,122 +5283,122 @@
         <v>83</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>427</v>
+        <v>206</v>
       </c>
       <c r="U41" s="7" t="s">
-        <v>428</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="D42" s="7">
         <v>2</v>
       </c>
       <c r="E42" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F42" s="7">
         <v>2</v>
       </c>
       <c r="G42" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H42" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42" s="7">
         <v>4</v>
       </c>
       <c r="J42" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" s="7">
         <v>4</v>
       </c>
       <c r="L42" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P42" s="7" t="s">
         <v>80</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="S42" s="7" t="s">
         <v>83</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="U42" s="7" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>403</v>
+        <v>607</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>404</v>
+        <v>196</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>405</v>
+        <v>608</v>
       </c>
       <c r="D43" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E43" s="7">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F43" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G43" s="7">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H43" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I43" s="7">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J43" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K43" s="7">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L43" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M43" s="7">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="N43" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O43" s="7">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="P43" s="7" t="s">
         <v>80</v>
@@ -5262,20 +5413,215 @@
         <v>83</v>
       </c>
       <c r="T43" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="D44" s="7">
+        <v>3</v>
+      </c>
+      <c r="E44" s="7">
+        <v>4</v>
+      </c>
+      <c r="F44" s="7">
+        <v>3</v>
+      </c>
+      <c r="G44" s="7">
+        <v>4</v>
+      </c>
+      <c r="H44" s="7">
+        <v>3</v>
+      </c>
+      <c r="I44" s="7">
+        <v>4</v>
+      </c>
+      <c r="J44" s="7">
+        <v>4</v>
+      </c>
+      <c r="K44" s="7">
+        <v>6</v>
+      </c>
+      <c r="L44" s="7">
+        <v>6</v>
+      </c>
+      <c r="M44" s="7">
+        <v>8</v>
+      </c>
+      <c r="N44" s="7">
+        <v>6</v>
+      </c>
+      <c r="O44" s="7">
+        <v>10</v>
+      </c>
+      <c r="P44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T44" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="D45" s="7">
+        <v>2</v>
+      </c>
+      <c r="E45" s="7">
+        <v>4</v>
+      </c>
+      <c r="F45" s="7">
+        <v>2</v>
+      </c>
+      <c r="G45" s="7">
+        <v>4</v>
+      </c>
+      <c r="H45" s="7">
+        <v>2</v>
+      </c>
+      <c r="I45" s="7">
+        <v>4</v>
+      </c>
+      <c r="J45" s="7">
+        <v>2</v>
+      </c>
+      <c r="K45" s="7">
+        <v>4</v>
+      </c>
+      <c r="L45" s="7">
+        <v>2</v>
+      </c>
+      <c r="M45" s="7">
+        <v>4</v>
+      </c>
+      <c r="N45" s="7">
+        <v>2</v>
+      </c>
+      <c r="O45" s="7">
+        <v>4</v>
+      </c>
+      <c r="P45" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R45" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T45" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D46" s="7">
+        <v>12</v>
+      </c>
+      <c r="E46" s="7">
+        <v>24</v>
+      </c>
+      <c r="F46" s="7">
+        <v>12</v>
+      </c>
+      <c r="G46" s="7">
+        <v>24</v>
+      </c>
+      <c r="H46" s="7">
+        <v>12</v>
+      </c>
+      <c r="I46" s="7">
+        <v>24</v>
+      </c>
+      <c r="J46" s="7">
+        <v>12</v>
+      </c>
+      <c r="K46" s="7">
+        <v>24</v>
+      </c>
+      <c r="L46" s="7">
+        <v>12</v>
+      </c>
+      <c r="M46" s="7">
+        <v>24</v>
+      </c>
+      <c r="N46" s="7">
+        <v>12</v>
+      </c>
+      <c r="O46" s="7">
+        <v>24</v>
+      </c>
+      <c r="P46" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q46" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R46" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="S46" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T46" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="U43" s="7" t="s">
+      <c r="U46" s="7" t="s">
         <v>407</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A37:U37"/>
+    <mergeCell ref="A38:U38"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A9:U9"/>
-    <mergeCell ref="A24:U24"/>
-    <mergeCell ref="A27:U27"/>
-    <mergeCell ref="A34:U34"/>
+    <mergeCell ref="A25:U25"/>
+    <mergeCell ref="A28:U28"/>
+    <mergeCell ref="A35:U35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7112,6 +7458,214 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8877AB15-A188-4364-B760-677088EE92F9}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="80.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>635</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>640</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>642</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>643</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>644</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>646</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>615</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>647</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>649</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7350,7 +7904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="664">
   <si>
     <t>ESTATES AI TOOL — PROGRAMME DURATION REFERENCE</t>
   </si>
@@ -653,7 +653,7 @@
     <t>FastTrack FT4 selected</t>
   </si>
   <si>
-    <t>Pre-procured framework (e.g. SCAPE, Pagabo). Fastest compliant route.</t>
+    <t/>
   </si>
   <si>
     <t>Project Type</t>
@@ -1280,7 +1280,7 @@
     <t>v4.5</t>
   </si>
   <si>
-    <t>Durations checked against eight University of Warwick projects (Oct 2026: Riley Court, Lakeside, Claycroft, Whitefields, Co-op, Scarman, IBRB café, Computer Science). Handover CH1 cut to 0–3 wks (commissioning runs inside construction; 2 wks on Lakeside, Riley Court and Whitefields). Fit-out CF2 S1–S4 shortened (Co-op 885 m² 7 wks; IBRB café ≈ 3 wks). M&amp;E refurb CR1 S1–S2 shortened (Scarman 5 wks). New size band S7 &gt; 10,000 m² with CR1 S7 50–70 (Claycroft 17,172 m²: 74 wks planned, forecast ≈ 95). Occupation and phasing uplifts no longer multiply — the higher applies (Lakeside: occupied, 6 sections, 45 wks). Confirmed unchanged: tender TN1 10–14 (Lakeside 13 wks to award), demolition CD1 (Whitefields ≈ 14 wks), CR1 S6 (Riley Court 36 + 6 wks strip-out), planning PL1 (Riley Court 7 wks).</t>
+    <t/>
   </si>
   <si>
     <t>S7_Lo</t>
@@ -1289,13 +1289,13 @@
     <t>S7_Hi</t>
   </si>
   <si>
-    <t>Full/partial services replacement. Longest refurb row — use when 3+ M&amp;E systems in q2_2. v4.5 (Oct 2026): S1–S2 shortened (Scarman toilets 71 m², 5-wk window); S7 (&gt;10,000 m²) added from Claycroft (17,172 m², Morgan Sindall: 74 wks works planned Jun 2025–Dec 2026, occupied, three blocks in turn). Riley Court 3,850 m² (S6): 36 wks + 6 wks strip-out = 42.</t>
-  </si>
-  <si>
-    <t>Standard offices/academic/retail/café. Partitions, ceiling, floor, M&amp;E 1st+2nd fix. v4.5 (Oct 2026): S1–S4 shortened — Co-op store 885 m² 7 wks (Kingfisher, 2 of them 7-day working), IBRB café 72 m² ≈ 3 wks (Senevo prelims).</t>
-  </si>
-  <si>
-    <t>Always added to construction. Snagging, Practical Completion, O&amp;M manuals and client move-in only — commissioning runs inside the last weeks of construction. v4.5 (Oct 2026): 2 wks on Lakeside (tender programme), Riley Court (Maris) and Whitefields (H&amp;S file); was up to 6-10 wks.</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Access mgmt, phasing, noise/dust, supervision. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
@@ -1304,7 +1304,7 @@
     <t>Partial decant / zoned works. v4.5: not stacked with PH-1 — the higher of the two applies.</t>
   </si>
   <si>
-    <t>Sequential handovers extend site duration. v4.5 (Oct 2026): when occupation (OCC-1/OCC-2) also applies, only the HIGHER of the two is used — they no longer multiply. Lakeside (occupied, 6 sections, 45 wks) ran about 10% slower than Riley Court vacant.</t>
+    <t/>
   </si>
   <si>
     <t>TN4</t>
@@ -1850,7 +1850,7 @@
     <t>v4.10</t>
   </si>
   <si>
-    <t>Duration review against the owner's projects (11 Oct 2026). Occupation uplift OCC-1 +15% (was 30%), OCC-2 +10% (was 20%): Lakeside occupied ran about 10% slower than vacant Riley Court; Claycroft now 73 weeks against 74 planned. Design uplifts DS3a 1 week, DS4a 1 up to 500 m² and 2 above (were up to 3 and 4; they fired on almost every project). Planning PL1 / PL4 8–10 up to 1,500 m² (minor, 8-week statutory) and 10–13 above (major); PL2 8–10 up to 1,500 m². Tender TN1 S1–S3 4–6 / 5–7 / 6–8. Construction CF2 S5–S6 12–18 / 18–28, CF1 S5–S6 16–24 / 24–36, CN1 S5 40–56, CN2 S3–S6 26–38 / 36–52 / 50–70 / 70–95, CE1 S5–S6 8–12 / 10–16. New Modifiers row ME-HEAVY (4) holds the threshold the code used. Unchanged and confirmed: CR1 (Riley Court 41 vs 42), CD1 (Whitefields 14), CF2 S1–S4 (Co-op 8 vs 7, IBRB 3), CH1.</t>
+    <t/>
   </si>
   <si>
     <t>TN5</t>
@@ -1985,13 +1985,43 @@
     <t>JCT ICD, JCT SBC + CDP</t>
   </si>
   <si>
-    <t>v4.11  ·  October 2026  ·  Nabil Kayali</t>
+    <t/>
   </si>
   <si>
     <t>v4.11</t>
   </si>
   <si>
     <t>Procurement routes follow the RIBA Plan of Work 2020 (11 Oct 2026). New sheet 'Procurement': for each route (PR1 Traditional, PR2 Design &amp; Build 1 Stage, PR3 Design &amp; Build 2 Stage, PR4 Management Contract / Construction Management, matched to the Procurement Reference by ID) the stage after which the contractor is brought in, who does Stage 4, whether the first tender runs alongside Stage 3, and the second-stage price row; and the contract effects (MW: Stages 3–4 replaced by DS34-MW; CDP: client's Stage 4 x 0.8). No overlap of Stage 4 and construction. New Durations rows TN5 (framework direct award), TN7 (second-stage price) and DS34-MW (minor works design and specification).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.12  ·  October 2026  ·  Nabil Kayali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durations checked against eight of the owner's real projects (Oct 2026: Projects A–H — residential, student-residence and academic refurbishments, a demolition, a retail fit-out, a café fit-out, a WC refurbishment and a decarbonisation refurbishment). Handover CH1 cut to 0–3 wks (commissioning runs inside construction; 2 wks on three of the projects). Fit-out CF2 S1–S4 shortened (an 885 m² retail fit-out took 7 wks; a small café about 3 wks). M&amp;E refurb CR1 S1–S2 shortened (a small WC refurbishment: 5 wks). New size band S7 &gt; 10,000 m² with CR1 S7 50–70 (a 17,000 m² occupied student-residence refurbishment: 74 wks planned, forecast about 95). Occupation and phasing uplifts no longer multiply — the higher applies (an occupied 6-section refurbishment: 45 wks). Confirmed unchanged: tender TN1 10–14 (13 wks to award on one project), demolition CD1 (about 14 wks), CR1 S6 (a 3,850 m² full refurbishment: 36 + 6 wks strip-out), planning PL1 (7 wks).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration review against the owner's projects (11 Oct 2026). Occupation uplift OCC-1 +15% (was 30%), OCC-2 +10% (was 20%): an occupied refurbishment (Project A) ran about 10% slower than a vacant one (Project H); Project D now 73 weeks against 74 planned. Design uplifts DS3a 1 week, DS4a 1 up to 500 m² and 2 above (were up to 3 and 4; they fired on almost every project). Planning PL1 / PL4 8–10 up to 1,500 m² (minor, 8-week statutory) and 10–13 above (major); PL2 8–10 up to 1,500 m². Tender TN1 S1–S3 4–6 / 5–7 / 6–8. Construction CF2 S5–S6 12–18 / 18–28, CF1 S5–S6 16–24 / 24–36, CN1 S5 40–56, CN2 S3–S6 26–38 / 36–52 / 50–70 / 70–95, CE1 S5–S6 8–12 / 10–16. New Modifiers row ME-HEAVY (4) holds the threshold the code used. Unchanged and confirmed: CR1 (Project H 41 vs 42), CD1 (Project C 14), CF2 S1–S4 (Project F 8 vs 7, Project G 3), CH1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-procured framework (e.g. a national construction framework). Fastest compliant route.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full/partial services replacement. Longest refurb row — use when 3+ M&amp;E systems in q2_2. v4.5 (Oct 2026): S1–S2 shortened (a 71 m² WC refurbishment, 5-wk window); S7 (&gt;10,000 m²) added from a 17,000 m² occupied student-residence refurbishment (74 wks works planned, three blocks in turn). A 3,850 m² full refurbishment (S6): 36 wks + 6 wks strip-out = 42.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard offices/academic/retail/café. Partitions, ceiling, floor, M&amp;E 1st+2nd fix. v4.5 (Oct 2026): S1–S4 shortened — an 885 m² retail fit-out took 7 wks (2 of them 7-day working), a 72 m² café about 3 wks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always added to construction. Snagging, Practical Completion, O&amp;M manuals and client move-in only — commissioning runs inside the last weeks of construction. v4.5 (Oct 2026): 2 wks on three of the owner's projects; was up to 6-10 wks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sequential handovers extend site duration. v4.5 (Oct 2026): when occupation (OCC-1/OCC-2) also applies, only the HIGHER of the two is used — they no longer multiply. An occupied 6-section refurbishment (45 wks) ran about 10% slower than a vacant one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence notes anonymised (16 Oct 2026). No duration, rule or modifier changed.</t>
   </si>
 </sst>
 </file>
@@ -2464,7 +2494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2482,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2788,7 +2818,7 @@
         <v>415</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>416</v>
+        <v>655</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2828,7 +2858,7 @@
         <v>605</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>606</v>
+        <v>656</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2837,6 +2867,14 @@
       </c>
       <c r="B50" s="2" t="s">
         <v>653</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -5286,7 +5324,7 @@
         <v>206</v>
       </c>
       <c r="U41" s="7" t="s">
-        <v>207</v>
+        <v>657</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5990,7 +6028,7 @@
         <v>80</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>419</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -6140,7 +6178,7 @@
         <v>80</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>420</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -6340,7 +6378,7 @@
         <v>80</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>421</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -6612,7 +6650,7 @@
         <v>286</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>424</v>
+        <v>661</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">

--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB142D3B-13B6-4D6B-A020-388DED8CE785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1994,7 +1989,7 @@
     <t>Procurement routes follow the RIBA Plan of Work 2020 (11 Oct 2026). New sheet 'Procurement': for each route (PR1 Traditional, PR2 Design &amp; Build 1 Stage, PR3 Design &amp; Build 2 Stage, PR4 Management Contract / Construction Management, matched to the Procurement Reference by ID) the stage after which the contractor is brought in, who does Stage 4, whether the first tender runs alongside Stage 3, and the second-stage price row; and the contract effects (MW: Stages 3–4 replaced by DS34-MW; CDP: client's Stage 4 x 0.8). No overlap of Stage 4 and construction. New Durations rows TN5 (framework direct award), TN7 (second-stage price) and DS34-MW (minor works design and specification).</t>
   </si>
   <si>
-    <t xml:space="preserve">v4.12  ·  October 2026  ·  Nabil Kayali</t>
+    <t xml:space="preserve">v4.12  ·  October 2026  ·  Projento</t>
   </si>
   <si>
     <t xml:space="preserve">Durations checked against eight of the owner's real projects (Oct 2026: Projects A–H — residential, student-residence and academic refurbishments, a demolition, a retail fit-out, a café fit-out, a WC refurbishment and a decarbonisation refurbishment). Handover CH1 cut to 0–3 wks (commissioning runs inside construction; 2 wks on three of the projects). Fit-out CF2 S1–S4 shortened (an 885 m² retail fit-out took 7 wks; a small café about 3 wks). M&amp;E refurb CR1 S1–S2 shortened (a small WC refurbishment: 5 wks). New size band S7 &gt; 10,000 m² with CR1 S7 50–70 (a 17,000 m² occupied student-residence refurbishment: 74 wks planned, forecast about 95). Occupation and phasing uplifts no longer multiply — the higher applies (an occupied 6-section refurbishment: 45 wks). Confirmed unchanged: tender TN1 10–14 (13 wks to award on one project), demolition CD1 (about 14 wks), CR1 S6 (a 3,850 m² full refurbishment: 36 + 6 wks strip-out), planning PL1 (7 wks).</t>
